--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136247634888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526052474976</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461597442627</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
@@ -71,31 +71,31 @@
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
     <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329612731934</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495943069458</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.135048866272</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272497177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584348678589</t>
@@ -128,70 +128,70 @@
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367023468018</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576999664307</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.0840940475464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6630992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929336547852</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007318496704</t>
@@ -200,43 +200,43 @@
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746404647827</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742097854614</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793292999268</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873592376709</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493801116943</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610546112061</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194770812988</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837146759033</t>
@@ -314,40 +314,40 @@
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187410354614</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756837844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">11.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822397232056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311544418335</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
@@ -416,31 +416,31 @@
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362749099731</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903129577637</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034671783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487354278564</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144037246704</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472585678101</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342456817627</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028238296509</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079921722412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334196090698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -662,34 +662,34 @@
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814115524292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305528640747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.925386428833</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.221118927002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785429000854</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542591094971</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.3951139450073</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525360107422</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839597702026</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773944854736</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.323091506958</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596740722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696826934814</t>
@@ -881,43 +881,43 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4918003082275</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781433105469</t>
+    <t xml:space="preserve">12.8781442642212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771644592285</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
@@ -998,31 +998,31 @@
     <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508302688599</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664497375488</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622016906738</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008110046387</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633573532104</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
     <t xml:space="preserve">13.705057144165</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706911087036</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
     <t xml:space="preserve">15.3174133300781</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.183051109314</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486869812012</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695363998413</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027439117432</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
     <t xml:space="preserve">15.5413541793823</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011856079102</t>
+    <t xml:space="preserve">10.3011846542358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355478286743</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177888870239</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166360855103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552434921265</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834266662598</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -1888,6 +1888,9 @@
   <si>
     <t xml:space="preserve">18</t>
   </si>
+  <si>
+    <t xml:space="preserve">18.1000003814697</t>
+  </si>
 </sst>
 </file>
 
@@ -66887,7 +66890,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6104513889</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>787</v>
@@ -66908,6 +66911,32 @@
         <v>624</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6187615741</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1518</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>625</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -56,100 +56,100 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136247634888</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095705032349</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719417572021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495943069458</t>
+    <t xml:space="preserve">10.6495971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272497177124</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.140754699707</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251649856567</t>
@@ -170,31 +170,31 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034315109253</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840969085693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6630992889404</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929365158081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990337371826</t>
   </si>
   <si>
     <t xml:space="preserve">11.249382019043</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515958786011</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472114562988</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187410354614</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756837844849</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588888168335</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -368,61 +368,61 @@
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034200668335</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822397232056</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.100510597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289838790894</t>
@@ -479,70 +479,70 @@
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034671783447</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246475219727</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837598800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436130523682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.637939453125</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982311248779</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342456817627</t>
+    <t xml:space="preserve">12.8342437744141</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271076202393</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028238296509</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979816436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334196090698</t>
+    <t xml:space="preserve">11.5334224700928</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.9062690734863</t>
@@ -653,34 +653,34 @@
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814115524292</t>
+    <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305528640747</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685361862183</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.221118927002</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962623596191</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176755905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839597702026</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
@@ -827,37 +827,37 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.323091506958</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596740722656</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922897338867</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635084152222</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059457778931</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781442642212</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342357635498</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766721725464</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908205032349</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191114425659</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756923675537</t>
+    <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
     <t xml:space="preserve">11.6761837005615</t>
@@ -986,43 +986,43 @@
     <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215595245361</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644863128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361953735352</t>
+    <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664497375488</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622016906738</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.6008110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664459228516</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1058,73 +1058,73 @@
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.705057144165</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185689926147</t>
+    <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560216903687</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.8548669815063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
     <t xml:space="preserve">15.3174133300781</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382646560669</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039005279541</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027439117432</t>
+    <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861415863037</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.5413522720337</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.4818935394287</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
     <t xml:space="preserve">14.8247499465942</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1256,40 +1256,40 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011846542358</t>
+    <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907613754272</t>
+    <t xml:space="preserve">10.3907604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3760919570923</t>
+    <t xml:space="preserve">11.376091003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896057128906</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
@@ -1346,37 +1346,37 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197256088257</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552434921265</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282150268555</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834266662598</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -66916,7 +66916,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6187615741</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1518</v>
@@ -66937,6 +66937,32 @@
         <v>625</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.649375</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>218</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>625</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461578369141</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095714569092</t>
@@ -80,46 +80,46 @@
     <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977228164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116609573364</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472030639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251649856567</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840969085693</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929365158081</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990337371826</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625333786011</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177116394043</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428279876709</t>
@@ -284,22 +284,22 @@
     <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,46 +308,46 @@
     <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.6669187545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683946609497</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.899772644043</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581489562988</t>
@@ -407,31 +407,31 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982948303223</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.4902677536011</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
@@ -455,52 +455,52 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391815185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.100510597229</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304136276245</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457807540894</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837598800659</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516429901123</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.637939453125</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
@@ -566,34 +566,34 @@
     <t xml:space="preserve">12.8342437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.610538482666</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.842529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979816436768</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334224700928</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.9062690734863</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714029312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685361862183</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756713867188</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531126022339</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376899719238</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796884536743</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176755905151</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591032028198</t>
+    <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.7928161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696846008301</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111112594604</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635065078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205797195435</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776519775391</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.534725189209</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761827468872</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
@@ -992,43 +992,43 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644863128662</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503408432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361944198608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622016906738</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008110046387</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664459228516</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842067718506</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706930160522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185699462891</t>
+    <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
     <t xml:space="preserve">14.3320846557617</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455993652344</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">15.8548669815063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174133300781</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965658187866</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486869812012</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861396789551</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413522720337</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614225387573</t>
+    <t xml:space="preserve">12.3614234924316</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853605270386</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149089813232</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177888870239</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386402130127</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.376091003418</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.003119468689</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197256088257</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
     <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6749362945557</t>
+    <t xml:space="preserve">12.67493724823</t>
   </si>
   <si>
     <t xml:space="preserve">12.2718458175659</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625772476196</t>
@@ -66942,7 +66942,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.649375</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>218</v>
@@ -66963,6 +66963,32 @@
         <v>625</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6429976852</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>419</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>624</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="627">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,67 +44,67 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681949615479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526023864746</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187166213989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719417572021</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326547622681</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977228164673</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.914665222168</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116609573364</t>
+    <t xml:space="preserve">10.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.836706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
@@ -203,34 +203,34 @@
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537645339966</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
@@ -263,76 +263,76 @@
     <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953882217407</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048969268799</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435659408569</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669187545776</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187410354614</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479494094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
@@ -356,40 +356,40 @@
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034172058105</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.899772644043</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581489562988</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858852386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982957839966</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413511276245</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391815185547</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078035354614</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304155349731</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209568023682</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457807540894</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713493347168</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
@@ -527,55 +527,55 @@
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982330322266</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271085739136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.610538482666</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939664840698</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
     <t xml:space="preserve">12.5442523956299</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.842529296875</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348203659058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571287155151</t>
@@ -662,37 +662,37 @@
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382617950439</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714029312134</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -707,58 +707,58 @@
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756713867188</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3453989028931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796884536743</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802631378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.3951120376587</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839569091797</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608243942261</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810863494873</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225158691406</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059438705444</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111112594604</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635065078735</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776519775391</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534725189209</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
@@ -914,37 +914,37 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,28 +956,28 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.719108581543</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761827468872</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
@@ -986,34 +986,34 @@
     <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215614318848</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503408432007</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361944198608</t>
+    <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622035980225</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664459228516</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363288879395</t>
+    <t xml:space="preserve">13.4363298416138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811162948608</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706930160522</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1112,40 +1112,40 @@
     <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548669815063</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726249694824</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278385162354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444437026978</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861396789551</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818935394287</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
     <t xml:space="preserve">14.8247489929199</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614234924316</t>
+    <t xml:space="preserve">12.361421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330772399902</t>
+    <t xml:space="preserve">9.85330867767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840137481689</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907604217529</t>
+    <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583330154419</t>
+    <t xml:space="preserve">11.9583339691162</t>
   </si>
   <si>
     <t xml:space="preserve">11.7791814804077</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,67 +1355,67 @@
     <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.67493724823</t>
+    <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718458175659</t>
+    <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -1891,6 +1891,9 @@
   <si>
     <t xml:space="preserve">18.1000003814697</t>
   </si>
+  <si>
+    <t xml:space="preserve">17.6000003814697</t>
+  </si>
 </sst>
 </file>
 
@@ -66968,7 +66971,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6429976852</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>419</v>
@@ -66989,6 +66992,32 @@
         <v>624</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6176967593</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>60</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>17.7000007629395</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>626</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681949615479</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187166213989</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875324249268</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.914665222168</t>
+    <t xml:space="preserve">10.9146680831909</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.135046005249</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584367752075</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
@@ -131,85 +131,85 @@
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.836706161499</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431516647339</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472030639648</t>
+    <t xml:space="preserve">11.0472002029419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251621246338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746433258057</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552433013916</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742078781128</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177116394043</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501190185547</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194799423218</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.028244972229</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479494094849</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457345962524</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581480026245</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
@@ -413,61 +413,61 @@
     <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858852386475</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778524398804</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982957839966</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413530349731</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.245044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.100510597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209539413452</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
@@ -485,52 +485,52 @@
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954372406006</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837598800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.414231300354</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271085739136</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105356216431</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348203659058</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -638,58 +638,58 @@
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.773699760437</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.8234128952026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
@@ -701,52 +701,52 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088134765625</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453989028931</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371162414551</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785429000854</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376909255981</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885515213013</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802631378174</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679595947266</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810863494873</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059438705444</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596759796143</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,37 +914,37 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196018218994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.976674079895</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615468978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.719108581543</t>
+    <t xml:space="preserve">11.7191114425659</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.547402381897</t>
+    <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215614318848</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799606323242</t>
   </si>
   <si>
     <t xml:space="preserve">14.914324760437</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1977205276489</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
     <t xml:space="preserve">13.9737825393677</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185689926147</t>
+    <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1118,40 +1118,40 @@
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278385162354</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1160,37 +1160,37 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1280,58 +1280,58 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907613754272</t>
+    <t xml:space="preserve">10.3907604217529</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583339691162</t>
+    <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
     <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135446548462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1343,19 +1343,19 @@
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
@@ -1367,28 +1367,28 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552415847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065849304199</t>
+    <t xml:space="preserve">10.7065839767456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296903610229</t>
+    <t xml:space="preserve">10.4296894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3373918533325</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.0757780075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911809921265</t>
+    <t xml:space="preserve">10.8911800384521</t>
   </si>
   <si>
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064598083496</t>
+    <t xml:space="preserve">11.9064588546753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -66997,7 +66997,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6176967593</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>60</v>
@@ -67018,6 +67018,32 @@
         <v>626</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493402778</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>805</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>610</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681949615479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553030014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461597442627</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095705032349</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
@@ -104,37 +104,37 @@
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146680831909</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.306565284729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116609573364</t>
   </si>
   <si>
-    <t xml:space="preserve">10.135046005249</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431516647339</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407556533813</t>
@@ -158,31 +158,31 @@
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472002029419</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251621246338</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034315109253</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993810653687</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">11.3746433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5063257217407</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.5384426116943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201688766479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -320,52 +320,52 @@
     <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596277236938</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275060653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545043945312</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917455673218</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822368621826</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581480026245</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180030822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778524398804</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413530349731</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807590484619</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6508588790894</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.100510597229</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150955200195</t>
@@ -470,37 +470,37 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209539413452</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
     <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954372406006</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -509,34 +509,34 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837598800659</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402334213257</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105356216431</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259601593018</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079912185669</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773699760437</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062671661377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554065704346</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471220016479</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531126022339</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376909255981</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968351364136</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045450210571</t>
   </si>
   <si>
     <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962604522705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.792818069458</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773944854736</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810882568359</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
     <t xml:space="preserve">13.2153787612915</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,34 +914,34 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196018218994</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478908538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615468978882</t>
+    <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191114425659</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069255828857</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074150085449</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799606323242</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
     <t xml:space="preserve">14.914324760437</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872953414917</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768720626831</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185699462891</t>
+    <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726259231567</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
@@ -1169,34 +1169,34 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788097381592</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058353424072</t>
+    <t xml:space="preserve">16.7058372497559</t>
   </si>
   <si>
     <t xml:space="preserve">16.3475322723389</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479068756104</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417278289795</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313035964966</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809608459473</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907604217529</t>
+    <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135446548462</t>
+    <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926952362061</t>
+    <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448173522949</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1343,67 +1343,67 @@
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270603179932</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552415847778</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
     <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282131195068</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065839767456</t>
+    <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296894073486</t>
+    <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3835401535034</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757780075073</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680746078491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911800384521</t>
+    <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
     <t xml:space="preserve">10.8450317382812</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064588546753</t>
+    <t xml:space="preserve">11.9064598083496</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -67023,7 +67023,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493402778</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>805</v>
@@ -67044,6 +67044,32 @@
         <v>610</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6034953704</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>832</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>17.1000003814697</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>610</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526023864746</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
@@ -107,58 +107,58 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
     <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472030639648</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942863464355</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864891052246</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -242,55 +242,55 @@
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990337371826</t>
   </si>
   <si>
     <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384454727173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201717376709</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895278930664</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194799423218</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -299,37 +299,37 @@
     <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253383636475</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676538467407</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282468795776</t>
@@ -338,82 +338,82 @@
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683946609497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267681121826</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822368621826</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457345962524</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180030822754</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858823776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.3778533935547</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413501739502</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
@@ -467,79 +467,79 @@
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.228982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713493347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654851913452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246446609497</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516410827637</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142322540283</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011016845703</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288307189941</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548328399658</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879758834839</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375997543335</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062700271606</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488431930542</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056962966919</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554075241089</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022529602051</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531126022339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371143341064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796913146973</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176755905151</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679595947266</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856809616089</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613981246948</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242370605469</t>
@@ -848,34 +848,34 @@
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182474136353</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353921890259</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696846008301</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781442642212</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913080215454</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903301239014</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
@@ -1016,58 +1016,58 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.60080909729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977195739746</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768720626831</t>
+    <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498426437378</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425088882446</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444427490234</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683788299561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.2131690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1241,40 +1241,40 @@
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1319,37 +1319,37 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822729110718</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239679336548</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031213760376</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
     <t xml:space="preserve">11.1521530151367</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -67072,7 +67072,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494791667</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1191</v>
@@ -67081,7 +67081,7 @@
         <v>17.5</v>
       </c>
       <c r="D2495" t="n">
-        <v>17.2000007629395</v>
+        <v>16.8999996185303</v>
       </c>
       <c r="E2495" t="n">
         <v>17.2999992370605</v>
@@ -67093,6 +67093,32 @@
         <v>606</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6232291667</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>341</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>16.7999992370605</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>608</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475095748901</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681968688965</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461587905884</t>
@@ -68,28 +68,28 @@
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.361138343811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431488037109</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966794967651</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472030639648</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007299423218</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
@@ -215,58 +215,58 @@
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.7231225967407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990337371826</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625314712524</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384454727173</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515958786011</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048969268799</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
@@ -314,49 +314,49 @@
     <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.8275060653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.8114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588869094849</t>
@@ -371,34 +371,34 @@
     <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034200668335</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.899772644043</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260320663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822368621826</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581489562988</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858823776245</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
@@ -470,28 +470,28 @@
     <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228982925415</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713493347168</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654851913452</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837598800659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">13.4142322540283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939664840698</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028238296509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011016845703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294025421143</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062700271606</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488431930542</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571306228638</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305509567261</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685342788696</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082416534424</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253873825073</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371143341064</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -743,28 +743,28 @@
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796913146973</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856809616089</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230895996094</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353921890259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596740722656</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696826934814</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205816268921</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625267028809</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756923675537</t>
+    <t xml:space="preserve">11.3756942749023</t>
   </si>
   <si>
     <t xml:space="preserve">11.6761846542358</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215595245361</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942493438721</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.60080909729</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1529331207275</t>
+    <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498426437378</t>
+    <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965667724609</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486888885498</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683788299561</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2131690979004</t>
+    <t xml:space="preserve">16.2131729125977</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861406326294</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058372497559</t>
+    <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
     <t xml:space="preserve">16.481897354126</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591121673584</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699119567871</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386383056641</t>
@@ -1337,40 +1337,40 @@
     <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
     <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
     <t xml:space="preserve">11.1521530151367</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912425994873</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833534240723</t>
+    <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -67098,7 +67098,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6232291667</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>341</v>
@@ -67119,6 +67119,32 @@
         <v>608</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.5838541667</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>255</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>16.8999996185303</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>606</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329593658447</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977247238159</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
@@ -134,31 +134,31 @@
     <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576971054077</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
@@ -179,43 +179,43 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708984375</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793292999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537654876709</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231254577637</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515958786011</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -290,25 +290,25 @@
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8676557540894</t>
@@ -317,55 +317,55 @@
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669149398804</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479522705078</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.8114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749458312988</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223865509033</t>
@@ -395,73 +395,73 @@
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311544418335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144037246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465225219727</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837608337402</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.637939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271076202393</t>
@@ -575,91 +575,91 @@
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442543029785</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868265151978</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259582519531</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294025421143</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079893112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062671661377</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305528640747</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471239089966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088163375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
@@ -758,37 +758,37 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951148986816</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773944854736</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496673583984</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313770294189</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353921890259</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781423568726</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342348098755</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913080215454</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074131011963</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786346435547</t>
@@ -998,16 +998,16 @@
     <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799606323242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351732254028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008110046387</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664468765259</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768720626831</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602668762207</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
     <t xml:space="preserve">13.7946310043335</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363288879395</t>
+    <t xml:space="preserve">13.4363279342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.5259046554565</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174142837524</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517803192139</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382656097412</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
     <t xml:space="preserve">15.6757164001465</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027477264404</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861396789551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
     <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907604217529</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">11.1969394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791805267334</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926952362061</t>
+    <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.1822719573975</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239698410034</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197256088257</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062099456787</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552415847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -67156,7 +67156,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6811111111</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1579</v>
@@ -67177,6 +67177,32 @@
         <v>627</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6742939815</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>536</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>16.7999992370605</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>609</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553030014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136219024658</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526042938232</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082197189331</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
@@ -86,73 +86,73 @@
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146680831909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509450912476</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431516647339</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.14075756073</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5063257217407</t>
@@ -224,91 +224,91 @@
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.044303894043</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158315658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873592376709</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428270339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194770812988</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -317,67 +317,67 @@
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472143173218</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545053482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267681121826</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.8997745513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.522385597229</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457345962524</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.100513458252</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150955200195</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654880523682</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136629104614</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516439437866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
@@ -560,67 +560,67 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271085739136</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425321578979</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348203659058</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879758834839</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068437576294</t>
@@ -653,46 +653,46 @@
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -740,55 +740,55 @@
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.0885515213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802631378174</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962604522705</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039751052856</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839569091797</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199714660645</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810882568359</t>
@@ -833,37 +833,37 @@
     <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.323091506958</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353921890259</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596750259399</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.534725189209</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4918003082275</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644863128662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942493438721</t>
@@ -1903,6 +1903,9 @@
   <si>
     <t xml:space="preserve">18.7000007629395</t>
   </si>
+  <si>
+    <t xml:space="preserve">17.8999996185303</t>
+  </si>
 </sst>
 </file>
 
@@ -67292,7 +67295,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6910300926</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>3932</v>
@@ -67313,6 +67316,32 @@
         <v>629</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6874074074</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>61</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>630</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475095748901</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553030014038</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526042938232</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146680831909</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
@@ -128,88 +128,88 @@
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.14075756073</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631021499634</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158315658569</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873620986938</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201717376709</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428270339966</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515958786011</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771606445312</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048969268799</t>
@@ -308,43 +308,43 @@
     <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669158935547</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756856918335</t>
@@ -353,49 +353,49 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545053482056</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997745513916</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180030822754</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
@@ -449,31 +449,31 @@
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.100513458252</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150955200195</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.5859775543213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
@@ -515,25 +515,25 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516439437866</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271085739136</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939664840698</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011045455933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294025421143</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068437576294</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305519104004</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022500991821</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885515213013</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">12.3536863327026</t>
@@ -770,25 +770,25 @@
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951148986816</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839569091797</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313770294189</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353921890259</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596750259399</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534725189209</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342357635498</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200902938843</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
@@ -992,67 +992,67 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644863128662</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4664487838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3622026443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7799606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.914324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7351741790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7799625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9143257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7351741790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6008110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4664468765259</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602668762207</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050561904907</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
@@ -1127,37 +1127,37 @@
     <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174142837524</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382656097412</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
     <t xml:space="preserve">15.6757164001465</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788097381592</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1256,28 +1256,28 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907604217529</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791805267334</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135446548462</t>
   </si>
   <si>
     <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
     <t xml:space="preserve">11.6448183059692</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
@@ -1346,13 +1346,13 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197256088257</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1370,34 +1370,34 @@
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
     <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552415847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104541778564</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
@@ -67321,7 +67321,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6874074074</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>61</v>
@@ -67342,6 +67342,32 @@
         <v>630</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6611574074</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>2286</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475095748901</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
@@ -113,37 +113,37 @@
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746433258057</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552433013916</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873620986938</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990337371826</t>
   </si>
   <si>
     <t xml:space="preserve">11.249382019043</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048969268799</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435659408569</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596248626709</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917455673218</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180030822754</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982948303223</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6508588790894</t>
@@ -461,22 +461,22 @@
     <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859775543213</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.224645614624</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436130523682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982330322266</t>
@@ -569,43 +569,43 @@
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939664840698</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011045455933</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548328399658</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -641,46 +641,46 @@
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.9062671661377</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554065704346</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
@@ -698,22 +698,22 @@
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531126022339</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -746,28 +746,28 @@
     <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885515213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045450210571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962604522705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679615020752</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
@@ -824,40 +824,40 @@
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313770294189</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182493209839</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493619918823</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,34 +914,34 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.148380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478908538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069255828857</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786346435547</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799606323242</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
     <t xml:space="preserve">14.914324760437</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872953414917</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768720626831</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185699462891</t>
+    <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726259231567</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
@@ -1169,34 +1169,34 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788097381592</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058353424072</t>
+    <t xml:space="preserve">16.7058372497559</t>
   </si>
   <si>
     <t xml:space="preserve">16.3475322723389</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479068756104</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417278289795</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313035964966</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809608459473</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907604217529</t>
+    <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135446548462</t>
+    <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926952362061</t>
+    <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448173522949</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1343,67 +1343,67 @@
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270603179932</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552415847778</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
     <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282131195068</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065839767456</t>
+    <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296894073486</t>
+    <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3835401535034</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757780075073</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680746078491</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911800384521</t>
+    <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
     <t xml:space="preserve">10.8450317382812</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064588546753</t>
+    <t xml:space="preserve">11.9064598083496</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -67347,25 +67347,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6611574074</v>
+        <v>45967.5961226852</v>
       </c>
       <c r="B2505" t="n">
-        <v>2286</v>
+        <v>183</v>
       </c>
       <c r="C2505" t="n">
-        <v>19</v>
+        <v>19.2000007629395</v>
       </c>
       <c r="D2505" t="n">
-        <v>17.5</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="E2505" t="n">
-        <v>17.5</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="F2505" t="n">
-        <v>18.7000007629395</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="G2505" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,91 +47,91 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617513656616</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526052474976</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065624237061</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611354827881</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
@@ -140,55 +140,55 @@
     <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.14075756073</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.2576971054077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034315109253</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6630992889404</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742097854614</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158315658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231254577637</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625314712524</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -275,52 +275,52 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194770812988</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.8676538467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669158935547</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
@@ -329,43 +329,43 @@
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749486923218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -398,61 +398,61 @@
     <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311515808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450456619263</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362749099731</t>
@@ -479,46 +479,46 @@
     <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136629104614</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.6465225219727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246475219727</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837627410889</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">12.8342437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939645767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079912185669</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334224700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814115524292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471239089966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685361862183</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371171951294</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
@@ -737,22 +737,22 @@
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691080093384</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.080265045166</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.353684425354</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874031066895</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951120376587</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922452926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.477970123291</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111103057861</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625267028809</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913080215454</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766721725464</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
@@ -1007,34 +1007,34 @@
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.660267829895</t>
+    <t xml:space="preserve">13.6602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706920623779</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726249694824</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278413772583</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934753417969</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757192611694</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861396789551</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
     <t xml:space="preserve">15.5413551330566</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205018997192</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1226,25 +1226,25 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614234924316</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042760848999</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197237014771</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.67493724823</t>
+    <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.4208784103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282150268555</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -1906,6 +1906,9 @@
   <si>
     <t xml:space="preserve">18.5</t>
   </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
 </sst>
 </file>
 
@@ -67347,27 +67350,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6838541667</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>2286</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>628</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>183</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>622</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>480</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>18.7999992370605</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>18.3999996185303</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>18.5</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>18.5</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>630</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6747569444</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>2172</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>631</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326519012451</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495952606201</t>
@@ -101,31 +101,31 @@
     <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584367752075</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611354827881</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031240463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576971054077</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
@@ -182,73 +182,73 @@
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6630992889404</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158315658569</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
@@ -257,43 +257,43 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177116394043</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -302,43 +302,43 @@
     <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253402709961</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676538467407</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749486923218</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -380,64 +380,64 @@
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.5223875045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311515808105</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107091903687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982957839966</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413520812988</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150955200195</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289838790894</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.5903158187866</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713493347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136629104614</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465225219727</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319488525391</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271057128906</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -575,25 +575,25 @@
     <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939645767212</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442514419556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259601593018</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762479782104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334224700928</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234128952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.997407913208</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814115524292</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471239089966</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371171951294</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.751389503479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679615020752</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922452926636</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608243942261</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359659194946</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496692657471</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596759796143</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903301239014</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351751327515</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602687835693</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050552368164</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425088882446</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
@@ -1121,55 +1121,55 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444437026978</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591121673584</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1226,25 +1226,25 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614225387573</t>
+    <t xml:space="preserve">12.361421585083</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969394683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135465621948</t>
+    <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926971435547</t>
+    <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.734393119812</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208784103394</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -1909,6 +1909,9 @@
   <si>
     <t xml:space="preserve">19</t>
   </si>
+  <si>
+    <t xml:space="preserve">19.2000007629395</t>
+  </si>
 </sst>
 </file>
 
@@ -67428,7 +67431,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6747569444</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>2172</v>
@@ -67449,6 +67452,32 @@
         <v>631</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.691087963</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>61</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>632</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681968688965</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461568832397</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095724105835</t>
@@ -77,88 +77,88 @@
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614458084106</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326519012451</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977228164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031240463257</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627956390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873592376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
     <t xml:space="preserve">11.249382019043</t>
@@ -251,40 +251,40 @@
     <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201688766479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.2895307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,52 +308,52 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012188911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
@@ -389,97 +389,97 @@
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223875045776</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107091903687</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.245044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.7391815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903158187866</t>
@@ -488,25 +488,25 @@
     <t xml:space="preserve">12.9034643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713493347168</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530746459961</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
@@ -518,25 +518,25 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436149597168</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148031234741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
@@ -566,43 +566,43 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271057128906</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768198013306</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442514419556</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276823043823</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259601593018</t>
+    <t xml:space="preserve">12.8259582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348203659058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762479782104</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -611,61 +611,61 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.773699760437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
@@ -674,46 +674,46 @@
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471239089966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714029312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082416534424</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">12.3536853790283</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.751389503479</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496673583984</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111112594604</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.749363899231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205806732178</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064352035522</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4918003082275</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625286102295</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0196018218994</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074150085449</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.3503408432007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361953735352</t>
+    <t xml:space="preserve">13.4361944198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.6937589645386</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1977214813232</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633583068848</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
@@ -1091,28 +1091,28 @@
     <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.2278413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757192611694</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444417953491</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861396789551</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8092994689941</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1241,10 +1241,10 @@
     <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042760848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3760919570923</t>
+    <t xml:space="preserve">11.376091003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
@@ -1346,19 +1346,19 @@
     <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
     <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6749362945557</t>
+    <t xml:space="preserve">12.67493724823</t>
   </si>
   <si>
     <t xml:space="preserve">12.2718467712402</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
     <t xml:space="preserve">11.1073656082153</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
     <t xml:space="preserve">10.793851852417</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988208770752</t>
+    <t xml:space="preserve">11.3988199234009</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373302459717</t>
+    <t xml:space="preserve">10.9373292922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -1912,6 +1912,9 @@
   <si>
     <t xml:space="preserve">19.2000007629395</t>
   </si>
+  <si>
+    <t xml:space="preserve">19.1000003814697</t>
+  </si>
 </sst>
 </file>
 
@@ -67457,7 +67460,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.691087963</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>61</v>
@@ -67478,6 +67481,32 @@
         <v>632</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6739583333</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>1291</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>633</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,34 +47,34 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553030014038</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.914665222168</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272506713867</t>
@@ -128,64 +128,64 @@
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.49937915802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631011962891</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070627212524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">11.9158315658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793321609497</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537654876709</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -248,28 +248,28 @@
     <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201717376709</t>
+    <t xml:space="preserve">10.9201726913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253402709961</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435659408569</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472133636475</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223865509033</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457374572754</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172613143921</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
@@ -458,22 +458,22 @@
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078016281128</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150955200195</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.228982925415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
@@ -485,67 +485,67 @@
     <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859775543213</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530746459961</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625814437866</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837627410889</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148031234741</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982330322266</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868265151978</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
@@ -605,49 +605,49 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548357009888</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334224700928</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.773699760437</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488451004028</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056934356689</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974088668823</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819852828979</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885515213013</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303973197937</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525379180908</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225158691406</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596759796143</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196018218994</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615468978882</t>
+    <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
     <t xml:space="preserve">11.7191114425659</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761846542358</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.5474004745483</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1019,37 +1019,37 @@
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351732254028</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.60080909729</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872953414917</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602687835693</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363279342651</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1103,46 +1103,46 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.496563911438</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444446563721</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861387252808</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309289932251</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.541356086731</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1205,25 +1205,25 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205018997192</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301507949829</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197237014771</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062099456787</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552415847778</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625791549683</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436626434326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834159851074</t>
+    <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7988815307617</t>
+    <t xml:space="preserve">10.798882484436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373908996582</t>
+    <t xml:space="preserve">10.3373918533325</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1478,16 +1478,16 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -67541,7 +67541,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6194675926</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>264</v>
@@ -67562,6 +67562,32 @@
         <v>634</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.3334375</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>630</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="637">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,100 +47,100 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617513656616</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719417572021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614419937134</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329612731934</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326547622681</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966785430908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.2031269073486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576999664307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -182,73 +182,73 @@
     <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6630992889404</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708984375</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910047531128</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063247680664</t>
+    <t xml:space="preserve">11.5063276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158315658569</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873592376709</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990337371826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347980499268</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384454727173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194770812988</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7712993621826</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479522705078</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756837844849</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545024871826</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
@@ -398,52 +398,52 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858852386475</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982976913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734689712524</t>
@@ -455,52 +455,52 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457836151123</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859775543213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275560379028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472604751587</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342437744141</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271076202393</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">12.6105356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425321578979</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348203659058</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
@@ -623,52 +623,52 @@
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979816436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334224700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773699760437</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.9062700271606</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
     <t xml:space="preserve">13.0082406997681</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785429000854</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
@@ -743,49 +743,49 @@
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796913146973</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045478820801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802631378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.353684425354</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039722442627</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.751389503479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.792818069458</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856809616089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773954391479</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.323091506958</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225177764893</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739492416382</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668111801147</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696846008301</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111103057861</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
@@ -887,46 +887,46 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064361572266</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781442642212</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -935,28 +935,28 @@
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615468978882</t>
+    <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191114425659</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049659729004</t>
@@ -968,73 +968,73 @@
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.5474004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079063415527</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.135705947876</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.5649785995483</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,31 +1043,31 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768701553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1118,58 +1118,58 @@
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278413772583</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.496563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027439117432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330772399902</t>
+    <t xml:space="preserve">9.85330867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963813781738</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042760848999</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583320617676</t>
+    <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
     <t xml:space="preserve">12.1822719573975</t>
@@ -1325,31 +1325,31 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.7343950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -1920,6 +1920,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -67622,7 +67625,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6820486111</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>90</v>
@@ -67643,6 +67646,32 @@
         <v>623</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.4654282407</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -50,31 +50,31 @@
     <t xml:space="preserve">11.5617513656616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553030014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719417572021</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600940704346</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
@@ -98,67 +98,67 @@
     <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146680831909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065624237061</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.135046005249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272525787354</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966785430908</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031269073486</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576999664307</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627956390381</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -188,79 +188,79 @@
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708984375</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5063276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793321609497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990337371826</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384454727173</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201688766479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
@@ -269,25 +269,25 @@
     <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501209259033</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.2895307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194789886475</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
@@ -344,58 +344,58 @@
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.923864364624</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457365036011</t>
@@ -413,70 +413,70 @@
     <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.6107091903687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982976913452</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078044891357</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.228982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859775543213</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954372406006</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275560379028</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472604751587</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105356216431</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768198013306</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.5276823043823</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259601593018</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348203659058</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879749298096</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979816436768</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334224700928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.375997543335</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062700271606</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819852828979</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305509567261</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714029312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088134765625</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968370437622</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885496139526</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045478820801</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802631378174</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.751389503479</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591012954712</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856809616089</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668111801147</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696846008301</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111103057861</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342367172241</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625267028809</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.191309928894</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761846542358</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474004745483</t>
+    <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -983,28 +983,28 @@
     <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079063415527</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649785995483</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622026443481</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977224349976</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768701553345</t>
+    <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842058181763</t>
@@ -1067,79 +1067,79 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.660267829895</t>
+    <t xml:space="preserve">13.6602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174142837524</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.496563911438</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517774581909</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444446563721</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027439117432</t>
+    <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861406326294</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
@@ -1310,37 +1310,37 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926952362061</t>
+    <t xml:space="preserve">12.0926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822710037231</t>
   </si>
   <si>
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343950271606</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166351318359</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208784103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834159851074</t>
+    <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7988815307617</t>
+    <t xml:space="preserve">10.798882484436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373908996582</t>
+    <t xml:space="preserve">10.3373918533325</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1478,16 +1478,16 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -67651,7 +67651,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.4654282407</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>25</v>
@@ -67672,6 +67672,32 @@
         <v>636</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6910648148</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>320</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>17.7999992370605</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>630</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475067138672</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526023864746</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461597442627</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187166213989</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082197189331</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146680831909</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
@@ -119,88 +119,88 @@
     <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584367752075</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.14075756073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966785430908</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
     <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
     <t xml:space="preserve">11.374641418457</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
     <t xml:space="preserve">11.2493810653687</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953882217407</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -323,25 +323,25 @@
     <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479503631592</t>
@@ -350,37 +350,37 @@
     <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545024871826</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
@@ -389,76 +389,76 @@
     <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413530349731</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457836151123</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
     <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487373352051</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654851913452</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530727386475</t>
@@ -512,34 +512,34 @@
     <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625814437866</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837598800659</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379384994507</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348203659058</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">12.1465473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -731,40 +731,40 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691080093384</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874031066895</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039751052856</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839569091797</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">12.477970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496673583984</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353921890259</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.749363899231</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205797195435</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">12.0196018218994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903291702271</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761827468872</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503408432007</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.5649766921997</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361944198608</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
     <t xml:space="preserve">13.6937599182129</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664459228516</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842067718506</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706930160522</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394193649292</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548669815063</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069900512695</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726249694824</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
     <t xml:space="preserve">15.227840423584</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695383071899</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861396789551</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541356086731</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818935394287</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301488876343</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614234924316</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907604217529</t>
+    <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563982009888</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,22 +1355,22 @@
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.67493724823</t>
+    <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718458175659</t>
+    <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436626434326</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645130157471</t>
@@ -67781,7 +67781,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6911226852</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>307</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475067138672</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681968688965</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461578369141</t>
@@ -68,58 +68,58 @@
     <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.0783853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977228164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.914665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065624237061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.14075756073</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031230926514</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443058013916</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384454727173</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.7953872680664</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048969268799</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676538467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6669158935547</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596277236938</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713003158569</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545024871826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -398,55 +398,55 @@
     <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311544418335</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413530349731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457836151123</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.585976600647</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144008636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148031234741</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442543029785</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259582519531</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348194122314</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.641131401062</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488451004028</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056934356689</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814144134521</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -680,46 +680,46 @@
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685361862183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
     <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691080093384</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376909255981</t>
+    <t xml:space="preserve">12.2376880645752</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968360900879</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.353684425354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874031066895</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608243942261</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -839,31 +839,31 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182474136353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353921890259</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596750259399</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064342498779</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.32008934021</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196018218994</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049640655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903291702271</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786327362061</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508321762085</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.60080909729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498426437378</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1112,55 +1112,55 @@
     <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
     <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726259231567</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444437026978</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1169,37 +1169,37 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683788299561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.213171005249</t>
+    <t xml:space="preserve">16.2131690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541356086731</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058353424072</t>
+    <t xml:space="preserve">16.7058372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479068756104</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809513092041</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1331,31 +1331,31 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.734393119812</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270603179932</t>
+    <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208793640137</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282131195068</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436626434326</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645130157471</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
     <t xml:space="preserve">11.768012046814</t>
@@ -1424,25 +1424,25 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -67805,6 +67805,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.3333333333</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>623</v>
+      </c>
+      <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681978225708</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.546160697937</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
     <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329584121704</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">10.6495971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146671295166</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.135046005249</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272506713867</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
@@ -137,76 +137,76 @@
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840940475464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746433258057</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -242,37 +242,37 @@
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814979553223</t>
+    <t xml:space="preserve">11.2815008163452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501209259033</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194780349731</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756837844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238615036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114500045776</t>
@@ -365,40 +365,40 @@
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.899772644043</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
@@ -437,79 +437,79 @@
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457807540894</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034671783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
     <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
@@ -539,73 +539,73 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.637939453125</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402334213257</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271057128906</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939645767212</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.842529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
@@ -617,22 +617,22 @@
     <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.641131401062</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334205627441</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371143341064</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542591094971</t>
@@ -770,40 +770,40 @@
     <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.3951120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.3039722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.751389503479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199705123901</t>
@@ -812,28 +812,28 @@
     <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613990783691</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810892105103</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -869,82 +869,82 @@
     <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064361572266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781442642212</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,34 +956,34 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761827468872</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074131011963</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.135705947876</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503408432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.6008110046387</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664468765259</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.705057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560216903687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1124,46 +1124,46 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174133300781</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695363998413</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1175,25 +1175,25 @@
     <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1205,19 +1205,19 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1226,34 +1226,34 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840137481689</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3760919570923</t>
+    <t xml:space="preserve">11.376091003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1322,43 +1322,43 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625772476196</t>
@@ -67862,7 +67862,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6847106481</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>1368</v>
@@ -67883,6 +67883,32 @@
         <v>636</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.5373958333</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>268</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>632</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475095748901</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681978225708</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
@@ -59,145 +59,145 @@
     <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.546160697937</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272525787354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611354827881</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.140754699707</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695476531982</t>
@@ -215,49 +215,49 @@
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231225967407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493801116943</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2815008163452</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201698303223</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771144866943</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194780349731</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837146759033</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756837844849</t>
+    <t xml:space="preserve">11.8756866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238615036011</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275060653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114500045776</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034191131592</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457345962524</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
@@ -458,49 +458,49 @@
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078016281128</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457807540894</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034671783447</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.5859775543213</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -515,40 +515,40 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516410827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148059844971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.4142322540283</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319507598877</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982311248779</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342456817627</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.842529296875</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093881607056</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -644,79 +644,79 @@
     <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056962966919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305500030518</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756742477417</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
     <t xml:space="preserve">12.088550567627</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -767,40 +767,40 @@
     <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874002456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.751389503479</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591012954712</t>
+    <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679615020752</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608224868774</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413837432861</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635084152222</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059457778931</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064361572266</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.534725189209</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342367172241</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.191309928894</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.933744430542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.976674079895</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908185958862</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756942749023</t>
   </si>
   <si>
     <t xml:space="preserve">11.6761837005615</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074131011963</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215614318848</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503408432007</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622016906738</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008110046387</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1529331207275</t>
+    <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498426437378</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.705057144165</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
@@ -1094,76 +1094,76 @@
     <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560216903687</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174133300781</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486869812012</t>
+    <t xml:space="preserve">15.0486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695363998413</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330772399902</t>
+    <t xml:space="preserve">9.85330867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1337,28 +1337,28 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
     <t xml:space="preserve">11.107364654541</t>
@@ -1388,22 +1388,22 @@
     <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282150268555</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1415,13 +1415,13 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,34 +1466,34 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -67888,7 +67888,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.5373958333</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>268</v>
@@ -67909,6 +67909,32 @@
         <v>632</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6910185185</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>622</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="639">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,43 +56,43 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
     <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783853530884</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495962142944</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977256774902</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.306565284729</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732925415039</t>
+    <t xml:space="preserve">11.273289680481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
@@ -203,100 +203,100 @@
     <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742097854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873620986938</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990337371826</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
     <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201688766479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177116394043</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501209259033</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
@@ -305,79 +305,79 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676567077637</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669149398804</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7712993621826</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479522705078</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.8114500045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588888168335</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749458312988</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997745513916</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180030822754</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982976913452</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413520812988</t>
@@ -446,34 +446,34 @@
     <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.100513458252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
@@ -515,46 +515,46 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472604751587</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436159133911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442543029785</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.5276823043823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093881607056</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116821289062</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288297653198</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
@@ -662,82 +662,82 @@
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371143341064</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -746,52 +746,52 @@
     <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885515213013</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874002456665</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282541275024</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951148986816</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.3039722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.751389503479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839597702026</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359687805176</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496692657471</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225177764893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413837432861</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635084152222</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776538848877</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534725189209</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488706588745</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781423568726</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483821868896</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625267028809</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.191309928894</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766721725464</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761846542358</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474004745483</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
@@ -980,64 +980,64 @@
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079063415527</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649785995483</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361953735352</t>
+    <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622016906738</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.60080909729</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977224349976</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706911087036</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174142837524</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517784118652</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444446563721</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027439117432</t>
+    <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788097381592</t>
+    <t xml:space="preserve">16.0788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,61 +1199,61 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
     <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093013763428</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.047908782959</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614225387573</t>
+    <t xml:space="preserve">12.361421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011846542358</t>
+    <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177888870239</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969394683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166351318359</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208784103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282150268555</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.793851852417</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7988815307617</t>
+    <t xml:space="preserve">10.798882484436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373908996582</t>
+    <t xml:space="preserve">10.3373918533325</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833534240723</t>
+    <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -1926,6 +1926,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5</t>
   </si>
 </sst>
 </file>
@@ -67992,7 +67995,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6909953704</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>2738</v>
@@ -68013,6 +68016,32 @@
         <v>637</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.676412037</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>1385</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>638</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,61 +44,61 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553058624268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512516021729</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187166213989</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719388961792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.0783853530884</t>
   </si>
   <si>
     <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875352859497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495943069458</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977247238159</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.306565284729</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584348678589</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576971054077</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732925415039</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
     <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631002426147</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5063257217407</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
@@ -230,34 +230,34 @@
     <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793321609497</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384426116943</t>
+    <t xml:space="preserve">11.5384454727173</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201707839966</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
@@ -296,37 +296,37 @@
     <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253383636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676567077637</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596277236938</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121879577637</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7712993621826</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756856918335</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749458312988</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464725494385</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -374,34 +374,34 @@
     <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.8997745513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260320663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
@@ -464,46 +464,46 @@
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304136276245</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.228982925415</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954343795776</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
@@ -512,25 +512,25 @@
     <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625814437866</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472604751587</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148031234741</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319488525391</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271066665649</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.641131401062</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062700271606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234128952026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
@@ -671,28 +671,28 @@
     <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819852828979</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -701,25 +701,25 @@
     <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685361862183</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082416534424</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088134765625</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022520065308</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.221118927002</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">12.088550567627</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045478820801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839597702026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.792818069458</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230895996094</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059438705444</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182474136353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596740722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696826934814</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064342498779</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342357635498</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
@@ -971,37 +971,37 @@
     <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474004745483</t>
+    <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
@@ -68076,7 +68076,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.5318171296</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>1301</v>
@@ -68097,6 +68097,32 @@
         <v>632</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6398148148</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>1092</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>19.6000003814697</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>633</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475095748901</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553030014038</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461578369141</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326547622681</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065624237061</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.1272497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.361138343811</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560426712036</t>
@@ -146,64 +146,64 @@
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966785430908</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864910125732</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007328033447</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
@@ -212,28 +212,28 @@
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493829727173</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625314712524</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253402709961</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676567077637</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472133636475</t>
@@ -326,22 +326,22 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479513168335</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275060653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -368,28 +368,28 @@
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545024871826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997716903687</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107091903687</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
@@ -482,25 +482,25 @@
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
     <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487344741821</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472576141357</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -563,37 +563,37 @@
     <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271085739136</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028238296509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
@@ -602,40 +602,40 @@
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
@@ -647,19 +647,19 @@
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382617950439</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719785690308</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
@@ -716,70 +716,70 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371162414551</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785438537598</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.751389503479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
@@ -791,103 +791,103 @@
     <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591032028198</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679624557495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922452926636</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739492416382</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668140411377</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353921890259</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064361572266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620363235474</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615468978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
     <t xml:space="preserve">11.6761837005615</t>
@@ -977,64 +977,64 @@
     <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508302688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,58 +1043,58 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768720626831</t>
+    <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633573532104</t>
+    <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498445510864</t>
+    <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1121,58 +1121,58 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.2278413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486869812012</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039005279541</t>
+    <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444437026978</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788059234619</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058372497559</t>
+    <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
     <t xml:space="preserve">16.3475322723389</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923206329346</t>
+    <t xml:space="preserve">16.3923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">16.6162586212158</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1223,28 +1223,28 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853624343872</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417278289795</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772457122803</t>
@@ -1253,22 +1253,22 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042760848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583330154419</t>
+    <t xml:space="preserve">11.9583320617676</t>
   </si>
   <si>
     <t xml:space="preserve">11.779182434082</t>
@@ -1319,16 +1319,16 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822729110718</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166360855103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1361,46 +1361,46 @@
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718458175659</t>
+    <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.4208784103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104541778564</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834159851074</t>
+    <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988208770752</t>
+    <t xml:space="preserve">11.3988199234009</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373302459717</t>
+    <t xml:space="preserve">10.9373292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7988815307617</t>
+    <t xml:space="preserve">10.798882484436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373908996582</t>
+    <t xml:space="preserve">10.3373918533325</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68154,13 +68154,13 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6912615741</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>245</v>
       </c>
       <c r="C2535" t="n">
-        <v>18.8999996185303</v>
+        <v>19.5</v>
       </c>
       <c r="D2535" t="n">
         <v>18.8999996185303</v>
@@ -68175,6 +68175,32 @@
         <v>638</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6911458333</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>1157</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>638</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681968688965</t>
+    <t xml:space="preserve">11.4681978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136238098145</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187166213989</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082216262817</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
@@ -95,40 +95,40 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065624237061</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272497177124</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367033004761</t>
@@ -140,67 +140,67 @@
     <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.0840940475464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631021499634</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929336547852</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007328033447</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063247680664</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793292999268</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625343322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
@@ -260,37 +260,37 @@
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610546112061</t>
+    <t xml:space="preserve">11.161057472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194770812988</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883716583252</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -317,31 +317,31 @@
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596277236938</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479513168335</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275060653687</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588888168335</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545024871826</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -428,55 +428,55 @@
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.245044708252</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.7391815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078044891357</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
@@ -494,16 +494,16 @@
     <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
     <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2530736923218</t>
@@ -515,55 +515,55 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246475219727</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
     <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319507598877</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342456817627</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271066665649</t>
@@ -578,43 +578,43 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028238296509</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548347473145</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488431930542</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571306228638</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814115524292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
@@ -701,34 +701,34 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022500991821</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371143341064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874002456665</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -785,46 +785,46 @@
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679624557495</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856809616089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810892105103</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668130874634</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696826934814</t>
@@ -875,55 +875,55 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064361572266</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.534725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781433105469</t>
+    <t xml:space="preserve">12.8781423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
     <t xml:space="preserve">12.191309928894</t>
@@ -932,13 +932,13 @@
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478927612305</t>
@@ -947,46 +947,46 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615468978882</t>
+    <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903272628784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756923675537</t>
+    <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
@@ -998,76 +998,76 @@
     <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.135705947876</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649785995483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508302688599</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.60080909729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977224349976</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278413772583</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517784118652</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027439117432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1202,28 +1202,28 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8093013763428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540887832642</t>
@@ -1232,61 +1232,61 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963813781738</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011856079102</t>
+    <t xml:space="preserve">10.3011846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042760848999</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177888870239</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583320617676</t>
+    <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
     <t xml:space="preserve">10.793851852417</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,34 +1463,34 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68180,7 +68180,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6911458333</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>1157</v>
@@ -68201,6 +68201,32 @@
         <v>638</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6909837963</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>373</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>638</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,52 +47,52 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553030014038</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461559295654</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495952606201</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
@@ -125,52 +125,52 @@
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.2576971054077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695447921753</t>
   </si>
   <si>
     <t xml:space="preserve">11.374641418457</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
     <t xml:space="preserve">11.249382019043</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771144866943</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.0282459259033</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.923864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588878631592</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545053482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
@@ -389,52 +389,52 @@
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223875045776</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107091903687</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -458,13 +458,13 @@
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078016281128</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457807540894</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903158187866</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713464736938</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530746459961</t>
+    <t xml:space="preserve">12.2530717849731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246446609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271057128906</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442514419556</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868284225464</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259601593018</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762479782104</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116830825806</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737016677856</t>
@@ -647,34 +647,34 @@
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.8234157562256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082416534424</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531126022339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.751389503479</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176746368408</t>
@@ -791,73 +791,73 @@
     <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351751327515</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.660267829895</t>
+    <t xml:space="preserve">13.6602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050552368164</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425088882446</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
@@ -1121,55 +1121,55 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1226,25 +1226,25 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208784103394</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -68258,7 +68258,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6592708333</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>56</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475095748901</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">11.4681949615479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082216262817</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600940704346</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329593658447</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.6807804107666</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.14075756073</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257700920105</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251640319824</t>
@@ -170,73 +170,73 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034343719482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552433013916</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742097854614</t>
+    <t xml:space="preserve">11.4742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.044303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
     <t xml:space="preserve">11.7231245040894</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625314712524</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201707839966</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
@@ -281,91 +281,91 @@
     <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253383636475</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669158935547</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756837844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588859558105</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -416,28 +416,28 @@
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413511276245</t>
@@ -446,28 +446,28 @@
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362749099731</t>
@@ -476,37 +476,37 @@
     <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
     <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.184497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654851913452</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530746459961</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
@@ -515,46 +515,46 @@
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625814437866</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.9516439437866</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.610538482666</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939664840698</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028257369995</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276823043823</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.842529296875</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879768371582</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
@@ -659,55 +659,55 @@
     <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056934356689</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554065704346</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.1714057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756713867188</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453998565674</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.221118927002</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376909255981</t>
+    <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.0885515213013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045459747314</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282541275024</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303973197937</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
@@ -785,31 +785,31 @@
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922452926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856781005859</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779691696167</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613962173462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
     <t xml:space="preserve">13.2153778076172</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
@@ -869,49 +869,49 @@
     <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488706588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
     <t xml:space="preserve">12.2342357635498</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.7191114425659</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.5474004745483</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503427505493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.5649785995483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1019,67 +1019,67 @@
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.705057144165</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1109,64 +1109,64 @@
     <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.5560216903687</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726259231567</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027439117432</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861415863037</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541356086731</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479068756104</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540878295898</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011856079102</t>
+    <t xml:space="preserve">10.3011846542358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355478286743</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177888870239</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.734393119812</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166360855103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
@@ -1367,55 +1367,55 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270603179932</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552434921265</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282131195068</t>
+    <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436626434326</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617513656616</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553030014038</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187194824219</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719388961792</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977228164673</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146671295166</t>
@@ -113,31 +113,31 @@
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638380050659</t>
@@ -146,46 +146,46 @@
     <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.2031269073486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576999664307</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.0840940475464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631011962891</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063247680664</t>
+    <t xml:space="preserve">11.5063276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493829727173</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625333786011</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428270339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968641281128</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435659408569</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -317,46 +317,46 @@
     <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472105026245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756866455078</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275060653687</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.8114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.6588869094849</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545043945312</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.899772644043</t>
+    <t xml:space="preserve">11.8997755050659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260320663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.522385597229</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
@@ -443,25 +443,25 @@
     <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078044891357</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.590313911438</t>
@@ -491,67 +491,67 @@
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859775543213</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530746459961</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144037246704</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275531768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837598800659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148031234741</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142322540283</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319488525391</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
@@ -560,61 +560,61 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402334213257</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028238296509</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868265151978</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259601593018</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979816436768</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056962966919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685361862183</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396596908569</t>
   </si>
   <si>
     <t xml:space="preserve">13.0082406997681</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756742477417</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">12.3371143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045450210571</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962623596191</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874031066895</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
@@ -776,79 +776,79 @@
     <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199686050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359659194946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613962173462</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313770294189</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225177764893</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059438705444</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -860,40 +860,40 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182474136353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059457778931</t>
+    <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064352035522</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781423568726</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913080215454</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.976674079895</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908185958862</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049640655518</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903291702271</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
@@ -1007,19 +1007,19 @@
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351732254028</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.60080909729</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1529331207275</t>
+    <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872953414917</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498426437378</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602687835693</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363279342651</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
@@ -1115,40 +1115,40 @@
     <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.496563911438</t>
+    <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444446563721</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861387252808</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309289932251</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205018997192</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301507949829</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330867767334</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1280,28 +1280,28 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166341781616</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062099456787</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552415847778</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625791549683</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645120620728</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834159851074</t>
+    <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912425994873</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -68284,7 +68284,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6388425926</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>112</v>
@@ -68305,6 +68305,32 @@
         <v>632</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.5989467593</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>934</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>628</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.0783853530884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197608947754</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.135046005249</t>
   </si>
   <si>
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509450912476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431488037109</t>
+    <t xml:space="preserve">10.7431516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.140754699707</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031269073486</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942844390869</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063276290894</t>
+    <t xml:space="preserve">11.5063247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.538444519043</t>
@@ -266,40 +266,40 @@
     <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501209259033</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428270339966</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968641281128</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -308,79 +308,79 @@
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472105026245</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669158935547</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756866455078</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464754104614</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267709732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997755050659</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260320663452</t>
@@ -389,34 +389,34 @@
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
@@ -485,73 +485,73 @@
     <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.5859775543213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
     <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530755996704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.6625785827637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275531768799</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472604751587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246475219727</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837598800659</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142322540283</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768198013306</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868265151978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259611129761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -611,31 +611,31 @@
     <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979816436768</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056962966919</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685361862183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396596908569</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.925386428833</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756742477417</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371143341064</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376880645752</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968360900879</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045450210571</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962623596191</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176727294922</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525388717651</t>
@@ -791,40 +791,40 @@
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591012954712</t>
+    <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679595947266</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199686050415</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810892105103</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059438705444</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -860,49 +860,49 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182474136353</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111122131348</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766721725464</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049640655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903291702271</t>
@@ -968,31 +968,31 @@
     <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761846542358</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498426437378</t>
+    <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706920623779</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965667724609</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486888885498</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.213171005249</t>
+    <t xml:space="preserve">16.2131729125977</t>
   </si>
   <si>
     <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309289932251</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
     <t xml:space="preserve">16.481897354126</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.047908782959</t>
@@ -1232,31 +1232,31 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865171432495</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166341781616</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
     <t xml:space="preserve">12.4509973526001</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
     <t xml:space="preserve">11.107364654541</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645120620728</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912425994873</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833534240723</t>
+    <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -68310,7 +68310,7 @@
     </row>
     <row r="2541">
       <c r="A2541" s="1" t="n">
-        <v>46021.5989467593</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2541" t="n">
         <v>934</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512554168701</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526042938232</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095705032349</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.914665222168</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472030639648</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993801116943</t>
@@ -194,46 +194,46 @@
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910076141357</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742097854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793321609497</t>
+    <t xml:space="preserve">11.7793292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428270339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771606445312</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194799423218</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435659408569</t>
+    <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121870040894</t>
@@ -338,124 +338,124 @@
     <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603628158569</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756837844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267681121826</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.8997745513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734718322754</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391843795776</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078035354614</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150955200195</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -476,79 +476,79 @@
     <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457807540894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.5903129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144037246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093900680542</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259601593018</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762479782104</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011026382446</t>
@@ -614,28 +614,28 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079921722412</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
@@ -647,79 +647,79 @@
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554094314575</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814115524292</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
@@ -734,37 +734,37 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779682159424</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059457778931</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630180358887</t>
+    <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478927612305</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.762038230896</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069236755371</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215595245361</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508302688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664497375488</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622016906738</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.6008110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633573532104</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
     <t xml:space="preserve">13.705057144165</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
     <t xml:space="preserve">13.5706911087036</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
     <t xml:space="preserve">15.3174133300781</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.183051109314</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695363998413</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444437026978</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027439117432</t>
+    <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
     <t xml:space="preserve">15.5413541793823</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3011846542358</t>
+    <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355478286743</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177888870239</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3760919570923</t>
+    <t xml:space="preserve">11.376091003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552434921265</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">10.9282150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834266662598</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988208770752</t>
+    <t xml:space="preserve">11.3988199234009</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373302459717</t>
+    <t xml:space="preserve">10.9373292922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -68337,6 +68337,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6693865741</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>810</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475067138672</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681949615479</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
@@ -53,64 +53,64 @@
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600950241089</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875314712524</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116580963135</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
@@ -131,46 +131,46 @@
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.0840969085693</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864900588989</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929365158081</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746433258057</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793292999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537645339966</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231254577637</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990365982056</t>
+    <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
@@ -254,31 +254,31 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501180648804</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253383636475</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676567077637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121870040894</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603666305542</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683927536011</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
     <t xml:space="preserve">11.8275079727173</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749477386475</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092351913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.217264175415</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245041847229</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.7391843795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.7150936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362768173218</t>
@@ -479,40 +479,40 @@
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457836151123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
     <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654851913452</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530746459961</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144037246704</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.6625804901123</t>
@@ -524,37 +524,37 @@
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479984283447</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436130523682</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982311248779</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939664840698</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.5276794433594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348194122314</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011016845703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288307189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879749298096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.641134262085</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.997407913208</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554075241089</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
     <t xml:space="preserve">13.0082406997681</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088153839111</t>
+    <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756723403931</t>
@@ -722,43 +722,43 @@
     <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376899719238</t>
+    <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885515213013</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045459747314</t>
+    <t xml:space="preserve">12.2045478820801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -767,43 +767,43 @@
     <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176755905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199705123901</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359659194946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810873031616</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493619918823</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -914,37 +914,37 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625286102295</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361953735352</t>
+    <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799606323242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.660267829895</t>
+    <t xml:space="preserve">13.6602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1097,46 +1097,46 @@
     <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185689926147</t>
+    <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
     <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455993652344</t>
+    <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726259231567</t>
+    <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278385162354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039005279541</t>
+    <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996562957764</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541356086731</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479068756104</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490644454956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,31 +1280,31 @@
     <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907613754272</t>
+    <t xml:space="preserve">10.3907604217529</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177907943726</t>
+    <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.734393119812</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270603179932</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552415847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282131195068</t>
+    <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436626434326</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065849304199</t>
+    <t xml:space="preserve">10.7065839767456</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296903610229</t>
+    <t xml:space="preserve">10.4296894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3373918533325</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757780075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911809921265</t>
+    <t xml:space="preserve">10.8911800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064598083496</t>
+    <t xml:space="preserve">11.9064588546753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68394,10 +68394,10 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6809143518</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C2544" t="n">
         <v>18.8999996185303</v>
@@ -68415,6 +68415,32 @@
         <v>641</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6792939815</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475067138672</t>
+    <t xml:space="preserve">11.6475095748901</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681949615479</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526023864746</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461578369141</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719417572021</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875324249268</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146671295166</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116580963135</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.556040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
@@ -179,73 +179,73 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840969085693</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746433258057</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443067550659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793292999268</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201707839966</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676567077637</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683927536011</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.8275089263916</t>
   </si>
   <si>
     <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749458312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034200668335</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267681121826</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
@@ -386,61 +386,61 @@
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092351913452</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457345962524</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180030822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866241455078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982957839966</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.245044708252</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391843795776</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078044891357</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -473,40 +473,40 @@
     <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457836151123</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903129577637</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
@@ -518,28 +518,28 @@
     <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379384994507</t>
@@ -548,64 +548,64 @@
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982311248779</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276794433594</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259601593018</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762460708618</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011016845703</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
@@ -614,34 +614,34 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288307189941</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879749298096</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.641134262085</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
     <t xml:space="preserve">11.947696685791</t>
@@ -665,64 +665,64 @@
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756713867188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785429000854</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045478820801</t>
+    <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542610168457</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874031066895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303973197937</t>
+    <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176755905151</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525379180908</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679595947266</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.7928161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608243942261</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199705123901</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -860,37 +860,37 @@
     <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493619918823</t>
+    <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059438705444</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488706588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781433105469</t>
+    <t xml:space="preserve">12.8781442642212</t>
   </si>
   <si>
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337463378906</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.976674079895</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049640655518</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903291702271</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
@@ -998,61 +998,61 @@
     <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622026443481</t>
+    <t xml:space="preserve">15.3622016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799606323242</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.6008110046387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664459228516</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498445510864</t>
+    <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602687835693</t>
+    <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050561904907</t>
@@ -1100,49 +1100,49 @@
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903877258301</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.8548669815063</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174133300781</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278385162354</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934772491455</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965648651123</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517793655396</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
     <t xml:space="preserve">15.6757164001465</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788097381592</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683807373047</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413522720337</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.4818935394287</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490644454956</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840232849121</t>
+    <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1286,34 +1286,34 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177888870239</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3760919570923</t>
+    <t xml:space="preserve">11.376091003418</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197256088257</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552415847778</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065839767456</t>
+    <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296894073486</t>
+    <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
     <t xml:space="preserve">10.3373918533325</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757780075073</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911800384521</t>
+    <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064588546753</t>
+    <t xml:space="preserve">11.9064598083496</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68420,7 +68420,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.6792939815</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>1296</v>
@@ -68441,6 +68441,32 @@
         <v>635</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.6909953704</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>629</v>
+      </c>
+      <c r="H2546" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="643">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475095748901</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -53,40 +53,40 @@
     <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187166213989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719417572021</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600950241089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875324249268</t>
@@ -101,70 +101,70 @@
     <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627918243408</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732906341553</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
@@ -185,46 +185,46 @@
     <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552433013916</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443067550659</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.7231254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771144866943</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515949249268</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771606445312</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
     <t xml:space="preserve">11.8194780349731</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048969268799</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253402709961</t>
+    <t xml:space="preserve">12.3253383636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187391281128</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596248626709</t>
   </si>
   <si>
     <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683927536011</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275089263916</t>
+    <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
     <t xml:space="preserve">11.811448097229</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749458312988</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464754104614</t>
+    <t xml:space="preserve">11.5464763641357</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
@@ -389,73 +389,73 @@
     <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180030822754</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420900344849</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866241455078</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143547058105</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508569717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150926589966</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
@@ -488,25 +488,25 @@
     <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
@@ -527,34 +527,34 @@
     <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.224645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939664840698</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.5276803970337</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -608,64 +608,64 @@
     <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548328399658</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294025421143</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079912185669</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305519104004</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471239089966</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756713867188</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453989028931</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022520065308</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211170196533</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785429000854</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">12.088550567627</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874031066895</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
@@ -785,25 +785,25 @@
     <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591032028198</t>
+    <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922443389893</t>
+    <t xml:space="preserve">12.8922433853149</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608243942261</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199705123901</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359659194946</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153797149658</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910949707031</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488706588745</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781442642212</t>
+    <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.3630170822144</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054563522339</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.719108581543</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069246292114</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074131011963</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786346435547</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503408432007</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1939,6 +1939,9 @@
   <si>
     <t xml:space="preserve">18.7999992370605</t>
   </si>
+  <si>
+    <t xml:space="preserve">19.2999992370605</t>
+  </si>
 </sst>
 </file>
 
@@ -68446,7 +68449,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6909953704</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>1006</v>
@@ -68467,6 +68470,32 @@
         <v>629</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6912268518</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>642</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681949615479</t>
+    <t xml:space="preserve">11.4681978225708</t>
   </si>
   <si>
     <t xml:space="preserve">11.5617504119873</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187166213989</t>
+    <t xml:space="preserve">11.2187194824219</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600950241089</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326547622681</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.306565284729</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170612335205</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
@@ -146,40 +146,40 @@
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627918243408</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864900588989</t>
@@ -191,67 +191,67 @@
     <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
     <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231254577637</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814989089966</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2771615982056</t>
@@ -296,25 +296,25 @@
     <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253383636475</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676538467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683927536011</t>
@@ -353,79 +353,79 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464763641357</t>
+    <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034200668335</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807619094849</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
@@ -464,28 +464,28 @@
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150926589966</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034671783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.224645614624</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436149597168</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733783721924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.610538482666</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.842529296875</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471239089966</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396606445312</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453989028931</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376899719238</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282541275024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
     <t xml:space="preserve">12.5525388717651</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922433853149</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">12.5359659194946</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -839,31 +839,31 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059438705444</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668140411377</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.7596759796143</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493619918823</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -920,31 +920,31 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478927612305</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.976674079895</t>
+    <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8908195495605</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.719108581543</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.547402381897</t>
+    <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074131011963</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786346435547</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357078552246</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503408432007</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942493438721</t>
+    <t xml:space="preserve">13.9942483901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4664487838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3622026443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7799606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.914324760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7351741790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7799615859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9143257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7351741790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6008110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4664459228516</t>
-  </si>
-  <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
     <t xml:space="preserve">13.9737825393677</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050561904907</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
@@ -1121,28 +1121,28 @@
     <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548669815063</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174133300781</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
     <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517793655396</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
     <t xml:space="preserve">15.6757164001465</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413522720337</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818935394287</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177888870239</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386402130127</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.376091003418</t>
+    <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
     <t xml:space="preserve">11.9583330154419</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135446548462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197256088257</t>
+    <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
@@ -1364,40 +1364,40 @@
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718458175659</t>
+    <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
     <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552425384521</t>
+    <t xml:space="preserve">11.5552415847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.152153968811</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065849304199</t>
+    <t xml:space="preserve">10.7065839767456</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296903610229</t>
+    <t xml:space="preserve">10.4296894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3373918533325</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757780075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911809921265</t>
+    <t xml:space="preserve">10.8911800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064598083496</t>
+    <t xml:space="preserve">11.9064588546753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68475,13 +68475,13 @@
     </row>
     <row r="2547">
       <c r="A2547" s="1" t="n">
-        <v>46031.6912268518</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2547" t="n">
         <v>1365</v>
       </c>
       <c r="C2547" t="n">
-        <v>19.1000003814697</v>
+        <v>19.2999992370605</v>
       </c>
       <c r="D2547" t="n">
         <v>18.2999992370605</v>
@@ -68496,6 +68496,32 @@
         <v>642</v>
       </c>
       <c r="H2547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="1" t="n">
+        <v>46034.4871527778</v>
+      </c>
+      <c r="B2548" t="n">
+        <v>680</v>
+      </c>
+      <c r="C2548" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="D2548" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2548" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="F2548" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>633</v>
+      </c>
+      <c r="H2548" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617513656616</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526023864746</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095705032349</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719398498535</t>
@@ -83,28 +83,28 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584348678589</t>
+    <t xml:space="preserve">10.1584377288818</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170621871948</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031269073486</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251649856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685033798218</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993801116943</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929365158081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
@@ -224,28 +224,28 @@
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231254577637</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990356445312</t>
+    <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
     <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -281,49 +281,49 @@
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953882217407</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771606445312</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253383636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472143173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596258163452</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
@@ -356,34 +356,34 @@
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114490509033</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749477386475</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997745513916</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
@@ -407,40 +407,40 @@
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982967376709</t>
+    <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807600021362</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.245044708252</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
@@ -470,28 +470,28 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362739562988</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034671783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625814437866</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516439437866</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479965209961</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436140060425</t>
@@ -545,52 +545,52 @@
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142293930054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982330322266</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.610538482666</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939645767212</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442514419556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.5276823043823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
@@ -617,25 +617,25 @@
     <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979816436768</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554065704346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902717590332</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453989028931</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376880645752</t>
+    <t xml:space="preserve">12.2376909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.0885486602783</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.080265045166</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282541275024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951120376587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679595947266</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810892105103</t>
+    <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059438705444</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488725662231</t>
@@ -914,40 +914,40 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478908538818</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766721725464</t>
+    <t xml:space="preserve">11.976674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.719108581543</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074150085449</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.135705947876</t>
+    <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351751327515</t>
@@ -1040,43 +1040,43 @@
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.660267829895</t>
+    <t xml:space="preserve">13.6602687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
     <t xml:space="preserve">13.7050552368164</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425088882446</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
@@ -1124,55 +1124,55 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695373535156</t>
+    <t xml:space="preserve">14.8695383071899</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683826446533</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1229,25 +1229,25 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1313,19 +1313,19 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135456085205</t>
+    <t xml:space="preserve">11.9135465621948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926971435547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208784103394</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -68634,7 +68634,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.4941898148</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>316</v>
@@ -68655,6 +68655,32 @@
         <v>643</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6910763889</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>419</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>632</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617513656616</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461597442627</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
@@ -86,19 +86,19 @@
     <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329612731934</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584377288818</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407556533813</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
     <t xml:space="preserve">11.0627937316895</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929365158081</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007299423218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070646286011</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9961280822754</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
     <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.1771144866943</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
@@ -275,70 +275,70 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.2895278930664</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968669891357</t>
+    <t xml:space="preserve">12.1968650817871</t>
   </si>
   <si>
     <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253383636475</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472143173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
@@ -353,40 +353,40 @@
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545043945312</t>
+    <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267700195312</t>
+    <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223865509033</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180021286011</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858852386475</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.6107091903687</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
@@ -440,82 +440,82 @@
     <t xml:space="preserve">11.5143547058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304155349731</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.228982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034671783447</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713474273682</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487344741821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654880523682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136629104614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625814437866</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
@@ -524,34 +524,34 @@
     <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472576141357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142293930054</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319507598877</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.2402334213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342456817627</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.610538482666</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
@@ -581,40 +581,40 @@
     <t xml:space="preserve">12.5442514419556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276823043823</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425302505493</t>
+    <t xml:space="preserve">12.842529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348175048828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548347473145</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079893112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.375994682312</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
@@ -650,34 +650,34 @@
     <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056934356689</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554065704346</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902717590332</t>
+    <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0305509567261</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088163375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453989028931</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785429000854</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885486602783</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045459747314</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">12.4282541275024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883957862854</t>
+    <t xml:space="preserve">12.8839569091797</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679595947266</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739511489868</t>
@@ -860,25 +860,25 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696836471558</t>
+    <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493619918823</t>
@@ -887,61 +887,61 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059448242188</t>
+    <t xml:space="preserve">12.4059457778931</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781433105469</t>
+    <t xml:space="preserve">12.8781423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.976674079895</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.719108581543</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.350341796875</t>
+    <t xml:space="preserve">13.3503408432007</t>
   </si>
   <si>
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.6008110046387</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664468765259</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842058181763</t>
+    <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6602687835693</t>
+    <t xml:space="preserve">13.6602668762207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0185689926147</t>
+    <t xml:space="preserve">14.0185699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903867721558</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934753417969</t>
+    <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517774581909</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382656097412</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444437026978</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.5413541793823</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591121673584</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3907613754272</t>
+    <t xml:space="preserve">10.3907604217529</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563982009888</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969394683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9135465621948</t>
+    <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926971435547</t>
+    <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
     <t xml:space="preserve">11.6448183059692</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.734393119812</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197256088257</t>
   </si>
   <si>
     <t xml:space="preserve">12.4957857131958</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1367,25 +1367,25 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104541778564</t>
   </si>
   <si>
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6295652389526</t>
+    <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757154464722</t>
+    <t xml:space="preserve">11.6757144927979</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
     <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219869613647</t>
+    <t xml:space="preserve">10.5219879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7065849304199</t>
+    <t xml:space="preserve">10.7065839767456</t>
   </si>
   <si>
     <t xml:space="preserve">11.0296277999878</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">10.6142864227295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4296903610229</t>
+    <t xml:space="preserve">10.4296894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3373918533325</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757780075073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8911809921265</t>
+    <t xml:space="preserve">10.8911800384521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9064598083496</t>
+    <t xml:space="preserve">11.9064588546753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8141622543335</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910558700562</t>
+    <t xml:space="preserve">12.0910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68660,13 +68660,13 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6910763889</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>419</v>
       </c>
       <c r="C2554" t="n">
-        <v>18.6000003814697</v>
+        <v>19</v>
       </c>
       <c r="D2554" t="n">
         <v>18.5</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681949615479</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082225799561</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095714569092</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875352859497</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326528549194</t>
+    <t xml:space="preserve">10.5326547622681</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495962142944</t>
@@ -101,43 +101,43 @@
     <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.914665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116580963135</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.361138343811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509479522705</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638389587402</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
     <t xml:space="preserve">11.0627927780151</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251621246338</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
@@ -173,22 +173,22 @@
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942873001099</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
@@ -197,49 +197,49 @@
     <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814989089966</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.161057472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895278930664</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428279876709</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837146759033</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596258163452</t>
@@ -332,22 +332,22 @@
     <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479503631592</t>
+    <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756837844849</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238634109497</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -374,34 +374,34 @@
     <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997745513916</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092323303223</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311525344849</t>
@@ -410,88 +410,88 @@
     <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617935180664</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866203308105</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982957839966</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508569717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150955200195</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304164886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.5903129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034643173218</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713493347168</t>
+    <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654861450195</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136657714844</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472576141357</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246475219727</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837627410889</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.951642036438</t>
@@ -539,34 +539,34 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436130523682</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148031234741</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342437744141</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271057128906</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028257369995</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093900680542</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762479782104</t>
+    <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011035919189</t>
+    <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548347473145</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.641131401062</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -641,28 +641,28 @@
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
     <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488431930542</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571277618408</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974088668823</t>
@@ -677,49 +677,49 @@
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685342788696</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082416534424</t>
+    <t xml:space="preserve">13.0082387924194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022520065308</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376880645752</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968360900879</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039741516113</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.8839588165283</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
     <t xml:space="preserve">12.7928171157837</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779691696167</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613962173462</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496683120728</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.331374168396</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230895996094</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413818359375</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325225830078</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668121337891</t>
+    <t xml:space="preserve">12.9668130874634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182474136353</t>
+    <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059457778931</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776529312134</t>
+    <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.4488716125488</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786327362061</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215595245361</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">13.1357069015503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3503427505493</t>
+    <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649785995483</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508321762085</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225402832031</t>
@@ -1028,34 +1028,34 @@
     <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799615859985</t>
+    <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6008100509644</t>
+    <t xml:space="preserve">14.60080909729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633583068848</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946300506592</t>
+    <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320837020874</t>
+    <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
     <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069910049438</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517793655396</t>
+    <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486888885498</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683788299561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.2131690979004</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861415863037</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309289932251</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">14.9591121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40543079376221</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957866668701</t>
   </si>
   <si>
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5552434921265</t>
+    <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5104551315308</t>
@@ -1391,28 +1391,28 @@
     <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834266662598</t>
+    <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436645507812</t>
+    <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68709,7 +68709,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6600462963</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>69</v>
@@ -68730,6 +68730,32 @@
         <v>635</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6911921296</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>35</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475067138672</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136228561401</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326547622681</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495971679688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.914665222168</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.361138343811</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170593261719</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638389587402</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251640319824</t>
+    <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732915878296</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840940475464</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993810653687</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
     <t xml:space="preserve">11.6631021499634</t>
@@ -194,46 +194,46 @@
     <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910047531128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158334732056</t>
+    <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493801116943</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347999572754</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814989089966</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">10.9201717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.161057472229</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177116394043</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895278930664</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647481918335</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253402709961</t>
+    <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472133636475</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187410354614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596258163452</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121879577637</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238634109497</t>
+    <t xml:space="preserve">11.9238615036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464754104614</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581489562988</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180030822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172613143921</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
     <t xml:space="preserve">11.3778533935547</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6107110977173</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
@@ -449,55 +449,55 @@
     <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304164886475</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903129577637</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
     <t xml:space="preserve">12.895435333252</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136657714844</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472595214844</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436130523682</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148050308228</t>
@@ -551,34 +551,34 @@
     <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342456817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939645767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288307189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879758834839</t>
+    <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079902648926</t>
@@ -635,70 +635,70 @@
     <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334215164185</t>
+    <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068437576294</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488431930542</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056943893433</t>
+    <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.997407913208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814125061035</t>
+    <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819862365723</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382617950439</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082387924194</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756713867188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3454008102417</t>
+    <t xml:space="preserve">12.3453998565674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022520065308</t>
+    <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531116485596</t>
+    <t xml:space="preserve">12.4531106948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376880645752</t>
+    <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">12.3536863327026</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282550811768</t>
+    <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.3951139450073</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176755905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525388717651</t>
   </si>
   <si>
     <t xml:space="preserve">12.8839588165283</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.7928161621094</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4779682159424</t>
+    <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.5773944854736</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810882568359</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739501953125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668130874634</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910978317261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922897338867</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635084152222</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205816268921</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5776538848877</t>
+    <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917984008789</t>
+    <t xml:space="preserve">12.4917993545532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8781433105469</t>
+    <t xml:space="preserve">12.8781442642212</t>
   </si>
   <si>
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625267028809</t>
+    <t xml:space="preserve">12.0625276565552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
     <t xml:space="preserve">12.3200912475586</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478908538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615488052368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191095352173</t>
+    <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756923675537</t>
+    <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761846542358</t>
+    <t xml:space="preserve">11.6761837005615</t>
   </si>
   <si>
     <t xml:space="preserve">11.5474014282227</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074150085449</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1357069015503</t>
+    <t xml:space="preserve">13.135705947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649785995483</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508321762085</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.60080909729</t>
+    <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
     <t xml:space="preserve">14.1529331207275</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">13.8842067718506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498426437378</t>
+    <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363288879395</t>
+    <t xml:space="preserve">13.4363298416138</t>
   </si>
   <si>
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425088882446</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560235977173</t>
+    <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.854868888855</t>
+    <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.2278385162354</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965667724609</t>
+    <t xml:space="preserve">15.4965658187866</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486888885498</t>
+    <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382637023926</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
     <t xml:space="preserve">15.9444427490234</t>
@@ -1169,34 +1169,34 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683788299561</t>
+    <t xml:space="preserve">16.1683807373047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2131690979004</t>
+    <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
     <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309289932251</t>
+    <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413541793823</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058372497559</t>
+    <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475341796875</t>
+    <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
     <t xml:space="preserve">16.481897354126</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205038070679</t>
+    <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591121673584</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.047908782959</t>
+    <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3614225387573</t>
+    <t xml:space="preserve">12.361421585083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853605270386</t>
+    <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
@@ -1241,40 +1241,40 @@
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313045501709</t>
+    <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
     <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772476196289</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330772399902</t>
+    <t xml:space="preserve">9.85330867767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963623046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149089813232</t>
+    <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40543079376221</t>
+    <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699119567871</t>
+    <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386383056641</t>
+    <t xml:space="preserve">10.8386392593384</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583330154419</t>
+    <t xml:space="preserve">11.9583339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896066665649</t>
+    <t xml:space="preserve">11.6896076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687562942505</t>
+    <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166341781616</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957866668701</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405731201172</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208793640137</t>
@@ -1376,19 +1376,19 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521530151367</t>
+    <t xml:space="preserve">11.1521520614624</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372676849365</t>
+    <t xml:space="preserve">11.5372667312622</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768012046814</t>
+    <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065223693848</t>
+    <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2142238616943</t>
+    <t xml:space="preserve">11.21422290802</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7988815307617</t>
+    <t xml:space="preserve">10.798882484436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2912425994873</t>
+    <t xml:space="preserve">10.291241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373908996582</t>
+    <t xml:space="preserve">10.3373918533325</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834775924683</t>
+    <t xml:space="preserve">10.9834785461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4911184310913</t>
+    <t xml:space="preserve">11.491117477417</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833534240723</t>
+    <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760427474976</t>
+    <t xml:space="preserve">11.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008020401001</t>
+    <t xml:space="preserve">11.5008029937744</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107061386108</t>
+    <t xml:space="preserve">11.3107051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156581878662</t>
+    <t xml:space="preserve">11.2156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404184341431</t>
+    <t xml:space="preserve">10.7404193878174</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354663848877</t>
+    <t xml:space="preserve">10.8354654312134</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.025562286377</t>
+    <t xml:space="preserve">11.0255632400513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057550430298</t>
+    <t xml:space="preserve">11.4057540893555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
+    <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235652923584</t>
+    <t xml:space="preserve">12.0235662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6413774490356</t>
+    <t xml:space="preserve">12.64137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938539505005</t>
+    <t xml:space="preserve">12.5938529968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68735,7 +68735,7 @@
     </row>
     <row r="2557">
       <c r="A2557" s="1" t="n">
-        <v>46045.6911921296</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2557" t="n">
         <v>35</v>
@@ -68756,6 +68756,32 @@
         <v>635</v>
       </c>
       <c r="H2557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="1" t="n">
+        <v>46048.6418865741</v>
+      </c>
+      <c r="B2558" t="n">
+        <v>121</v>
+      </c>
+      <c r="C2558" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2558" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2558" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2558" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475067138672</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681968688965</t>
+    <t xml:space="preserve">11.4681978225708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512544631958</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461568832397</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187175750732</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600921630859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875343322754</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495943069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116600036621</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584367752075</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611354827881</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367052078247</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.5560426712036</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627927780151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251630783081</t>
@@ -170,28 +170,28 @@
     <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840940475464</t>
+    <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631021499634</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
     <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961271286011</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443058013916</t>
@@ -230,70 +230,70 @@
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537635803223</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384454727173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201717376709</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501190185547</t>
+    <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895288467407</t>
+    <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647491455078</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837156295776</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713012695312</t>
+    <t xml:space="preserve">11.7712993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683927536011</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479522705078</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238615036011</t>
+    <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749458312988</t>
+    <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267681121826</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260320663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223846435547</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180030822754</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.2172622680664</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420890808105</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005125045776</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
@@ -497,40 +497,40 @@
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487363815308</t>
+    <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465196609497</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516429901123</t>
@@ -539,46 +539,46 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436159133911</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379365921021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319507598877</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342456817627</t>
+    <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939645767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288307189941</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879768371582</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759965896606</t>
+    <t xml:space="preserve">11.3759956359863</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
@@ -647,85 +647,85 @@
     <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068418502808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234128952026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819852828979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305500030518</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719795227051</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051197052002</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082397460938</t>
+    <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756713867188</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531106948853</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.353684425354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951139450073</t>
+    <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303973197937</t>
+    <t xml:space="preserve">12.3039722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513914108276</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176755905151</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525388717651</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928161621094</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496673583984</t>
+    <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230905532837</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596750259399</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910978317261</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922897338867</t>
+    <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347261428833</t>
+    <t xml:space="preserve">12.5347270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488716125488</t>
+    <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483812332153</t>
+    <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0196008682251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478908538818</t>
+    <t xml:space="preserve">11.8478918075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615488052368</t>
+    <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
     <t xml:space="preserve">11.7191104888916</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903291702271</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639987945557</t>
+    <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
     <t xml:space="preserve">13.0069246292114</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079044342041</t>
+    <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644872665405</t>
@@ -1004,37 +1004,37 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361953735352</t>
+    <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664478302002</t>
+    <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.928994178772</t>
+    <t xml:space="preserve">13.9289951324463</t>
   </si>
   <si>
     <t xml:space="preserve">14.0633583068848</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737825393677</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278385162354</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830520629883</t>
+    <t xml:space="preserve">15.183051109314</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965658187866</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382637023926</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039005279541</t>
+    <t xml:space="preserve">15.0039014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444417953491</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788078308105</t>
+    <t xml:space="preserve">16.0788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235942840576</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">15.7205057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247489929199</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540887832642</t>
+    <t xml:space="preserve">12.8540897369385</t>
   </si>
   <si>
     <t xml:space="preserve">12.361421585083</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
     <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963623046875</t>
+    <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042741775513</t>
+    <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969394683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583339691162</t>
+    <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
     <t xml:space="preserve">11.7791814804077</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448183059692</t>
+    <t xml:space="preserve">11.6448192596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957857131958</t>
+    <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
     <t xml:space="preserve">12.4062118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.4208784103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
     <t xml:space="preserve">11.1521520614624</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7938508987427</t>
+    <t xml:space="preserve">10.793851852417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8834257125854</t>
@@ -68761,7 +68761,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6418865741</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>121</v>
@@ -68782,6 +68782,32 @@
         <v>635</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.5805787037</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>172</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>640</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681978225708</t>
+    <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617513656616</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553049087524</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461568832397</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187175750732</t>
+    <t xml:space="preserve">11.2187166213989</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719388961792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
     <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495943069458</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
@@ -107,43 +107,43 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
     <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611354827881</t>
+    <t xml:space="preserve">10.361138343811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407566070557</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031259536743</t>
+    <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
     <t xml:space="preserve">11.0627927780151</t>
@@ -164,46 +164,46 @@
     <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732906341553</t>
+    <t xml:space="preserve">11.2732925415039</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708965301514</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746404647827</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.5063247680664</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158315658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537635803223</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873601913452</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384454727173</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647491455078</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.867654800415</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472114562988</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6669178009033</t>
@@ -326,40 +326,40 @@
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596277236938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7712993621826</t>
+    <t xml:space="preserve">11.7713003158569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683937072754</t>
+    <t xml:space="preserve">12.0683927536011</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756837844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.827507019043</t>
+    <t xml:space="preserve">11.8275060653687</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588869094849</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545024871826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260320663452</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.578592300415</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092332839966</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.361795425415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.6107120513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866222381592</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150945663452</t>
+    <t xml:space="preserve">11.7150955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304145812988</t>
+    <t xml:space="preserve">11.5304136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289848327637</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903129577637</t>
   </si>
   <si>
     <t xml:space="preserve">12.9034652709961</t>
@@ -491,22 +491,22 @@
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844997406006</t>
+    <t xml:space="preserve">13.1845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487373352051</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136648178101</t>
@@ -515,22 +515,22 @@
     <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.6625814437866</t>
   </si>
   <si>
     <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
     <t xml:space="preserve">12.9516429901123</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436159133911</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379365921021</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982330322266</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2402353286743</t>
+    <t xml:space="preserve">13.240234375</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
     <t xml:space="preserve">12.6105365753174</t>
@@ -599,25 +599,25 @@
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348203659058</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265329360962</t>
+    <t xml:space="preserve">12.7265338897705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">12.1879768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979825973511</t>
+    <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
     <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.6411323547363</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334205627441</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">11.7737007141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571296691895</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">11.7819852828979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382637023926</t>
+    <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719776153564</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">12.9088134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
     <t xml:space="preserve">12.0968351364136</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
     <t xml:space="preserve">12.353684425354</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3039722442627</t>
+    <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176746368408</t>
+    <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525379180908</t>
+    <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
@@ -803,58 +803,58 @@
     <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608224868774</t>
+    <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856790542603</t>
+    <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359668731689</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613971710205</t>
+    <t xml:space="preserve">12.4613981246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810892105103</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
     <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059438705444</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">13.1325235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739492416382</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668130874634</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
     <t xml:space="preserve">12.7922887802124</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064361572266</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347270965576</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615468978882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.135705947876</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361963272095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622035980225</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081447601318</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.2278413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965658187866</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1199,55 +1199,55 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923206329346</t>
+    <t xml:space="preserve">16.3923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042760848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583330154419</t>
+    <t xml:space="preserve">11.9583320617676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166360855103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208784103394</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
     <t xml:space="preserve">11.1073656082153</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988208770752</t>
+    <t xml:space="preserve">11.3988199234009</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373302459717</t>
+    <t xml:space="preserve">10.9373292922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -68787,7 +68787,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.5805787037</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>172</v>
@@ -68808,6 +68808,32 @@
         <v>640</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6376157407</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>205</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>630</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="644">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553030014038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136219024658</t>
@@ -65,61 +65,61 @@
     <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095724105835</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783882141113</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875324249268</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807794570923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.9146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065633773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584367752075</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367042541504</t>
+    <t xml:space="preserve">10.8367033004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.556040763855</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.14075756073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472021102905</t>
+    <t xml:space="preserve">11.0472011566162</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251640319824</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.084095954895</t>
+    <t xml:space="preserve">12.0840969085693</t>
   </si>
   <si>
     <t xml:space="preserve">11.6864881515503</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007318496704</t>
+    <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695466995239</t>
+    <t xml:space="preserve">11.5695457458496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070655822754</t>
@@ -224,28 +224,28 @@
     <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443048477173</t>
+    <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.9158325195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793302536011</t>
+    <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873601913452</t>
+    <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.7231254577637</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5625324249268</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.538444519043</t>
+    <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.7632713317871</t>
@@ -278,31 +278,31 @@
     <t xml:space="preserve">11.289529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515958786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771625518799</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968669891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253383636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
@@ -311,43 +311,43 @@
     <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640102386475</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187410354614</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
     <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238634109497</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">11.8275079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.811448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749477386475</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545034408569</t>
+    <t xml:space="preserve">11.5545024871826</t>
   </si>
   <si>
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997745513916</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785913467407</t>
+    <t xml:space="preserve">11.578592300415</t>
   </si>
   <si>
     <t xml:space="preserve">11.522385597229</t>
@@ -395,76 +395,76 @@
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172613143921</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778553009033</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866222381592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982957839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413530349731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391843795776</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078016281128</t>
+    <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.100510597229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304145812988</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">13.2487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954343795776</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654880523682</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662579536438</t>
+    <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472585678101</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516410827637</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148031234741</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8342447280884</t>
+    <t xml:space="preserve">12.8342437744141</t>
   </si>
   <si>
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105356216431</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939645767212</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
     <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
@@ -596,40 +596,40 @@
     <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259582519531</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7762470245361</t>
+    <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294025421143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079902648926</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411323547363</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488441467285</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554084777832</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">11.8814134597778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7902708053589</t>
+    <t xml:space="preserve">11.7902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">11.7819862365723</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714029312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465473175049</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051206588745</t>
+    <t xml:space="preserve">12.1051216125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685361862183</t>
+    <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
     <t xml:space="preserve">13.0082416534424</t>
@@ -713,49 +713,49 @@
     <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088144302368</t>
+    <t xml:space="preserve">12.9088153839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8756732940674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371162414551</t>
+    <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.221118927002</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.5691080093384</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968370437622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796884536743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
@@ -764,43 +764,43 @@
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951148986816</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.792818069458</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608243942261</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856800079346</t>
+    <t xml:space="preserve">12.5856790542603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4779691696167</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">12.5773935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0496683120728</t>
+    <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225177764893</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153778076172</t>
+    <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596769332886</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
     <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.32008934021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0196018218994</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337453842163</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903301239014</t>
+    <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3756923675537</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074140548706</t>
+    <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215614318848</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649766921997</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">14.4664468765259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1977205276489</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842067718506</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
     <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1103,46 +1103,46 @@
     <t xml:space="preserve">14.0185689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3320846557617</t>
+    <t xml:space="preserve">14.3320837020874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.556022644043</t>
+    <t xml:space="preserve">14.5560235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2726268768311</t>
+    <t xml:space="preserve">15.2726259231567</t>
   </si>
   <si>
     <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235961914062</t>
+    <t xml:space="preserve">16.1235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.5861415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.541356086731</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
     <t xml:space="preserve">16.6162586212158</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.0479068756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301488876343</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.77840137481689</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0177898406982</t>
+    <t xml:space="preserve">11.0177907943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.1969404220581</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.734393119812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">12.2718467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509973526001</t>
+    <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270593643188</t>
+    <t xml:space="preserve">12.2270603179932</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208793640137</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.107364654541</t>
+    <t xml:space="preserve">11.1073656082153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.152153968811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9282140731812</t>
+    <t xml:space="preserve">10.9282131195068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7938508987427</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436626434326</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645130157471</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629566192627</t>
+    <t xml:space="preserve">11.6295652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6757144927979</t>
+    <t xml:space="preserve">11.6757154464722</t>
   </si>
   <si>
     <t xml:space="preserve">11.35267162323</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">11.3065214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5219879150391</t>
+    <t xml:space="preserve">10.5219869613647</t>
   </si>
   <si>
     <t xml:space="preserve">10.7065849304199</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,13 +1511,13 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9987573623657</t>
+    <t xml:space="preserve">11.99875831604</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910568237305</t>
+    <t xml:space="preserve">12.0910558700562</t>
   </si>
   <si>
     <t xml:space="preserve">12.0710897445679</t>
@@ -1942,6 +1942,9 @@
   <si>
     <t xml:space="preserve">18.3999996185303</t>
   </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
 </sst>
 </file>
 
@@ -68891,13 +68894,13 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6910648148</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>99</v>
       </c>
       <c r="C2563" t="n">
-        <v>18.7000007629395</v>
+        <v>19.1000003814697</v>
       </c>
       <c r="D2563" t="n">
         <v>18.7000007629395</v>
@@ -68912,6 +68915,32 @@
         <v>633</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6597453704</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>2336</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>643</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -47,52 +47,52 @@
     <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136238098145</t>
+    <t xml:space="preserve">11.4136219024658</t>
   </si>
   <si>
     <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082206726074</t>
+    <t xml:space="preserve">11.0082197189331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095705032349</t>
+    <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600921630859</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614448547363</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
     <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326547622681</t>
+    <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
     <t xml:space="preserve">10.6495962142944</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.135048866272</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611354827881</t>
+    <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509450912476</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638380050659</t>
@@ -149,49 +149,49 @@
     <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251630783081</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2732925415039</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034315109253</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0840950012207</t>
+    <t xml:space="preserve">12.084095954895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007318496704</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374641418457</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552433013916</t>
+    <t xml:space="preserve">11.7552423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742097854614</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7070646286011</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814989089966</t>
+    <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.5384435653687</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610546112061</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771144866943</t>
+    <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
     <t xml:space="preserve">11.450119972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515968322754</t>
@@ -290,55 +290,55 @@
     <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968679428101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435678482056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472114562988</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.028244972229</t>
+    <t xml:space="preserve">12.0282459259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7712993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603656768799</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.0683937072754</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749458312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034200668335</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8997735977173</t>
+    <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917436599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092332839966</t>
+    <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581499099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
@@ -410,22 +410,22 @@
     <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172632217407</t>
+    <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420881271362</t>
+    <t xml:space="preserve">11.4420909881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5866212844849</t>
@@ -434,49 +434,49 @@
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902667999268</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413530349731</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807600021362</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450428009033</t>
+    <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508588790894</t>
+    <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078035354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005125045776</t>
+    <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5304155349731</t>
+    <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457817077637</t>
@@ -485,70 +485,70 @@
     <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713464736938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.184497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
     <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275541305542</t>
+    <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2246465682983</t>
+    <t xml:space="preserve">13.2246446609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479955673218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379375457764</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4142303466797</t>
+    <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2319498062134</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.240234375</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271066665649</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868274688721</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">12.8425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348203659058</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -608,67 +608,67 @@
     <t xml:space="preserve">12.8011026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
     <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288288116455</t>
+    <t xml:space="preserve">12.3288297653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294034957886</t>
+    <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8979835510254</t>
+    <t xml:space="preserve">11.8979825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079912185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411323547363</t>
+    <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737007141113</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234128952026</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974088668823</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
@@ -683,115 +683,115 @@
     <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1382627487183</t>
+    <t xml:space="preserve">12.1382617950439</t>
   </si>
   <si>
     <t xml:space="preserve">12.0719776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471229553223</t>
+    <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714038848877</t>
+    <t xml:space="preserve">12.1714029312134</t>
   </si>
   <si>
     <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1051216125488</t>
+    <t xml:space="preserve">12.1051197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.221118927002</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5691089630127</t>
+    <t xml:space="preserve">12.569109916687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376899719238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
     <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796913146973</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542591094971</t>
+    <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.353684425354</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4282560348511</t>
+    <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951148986816</t>
+    <t xml:space="preserve">12.3951120376587</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7513904571533</t>
+    <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176746368408</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591012954712</t>
+    <t xml:space="preserve">12.8591032028198</t>
   </si>
   <si>
     <t xml:space="preserve">12.7679605484009</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">12.5608234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199705123901</t>
+    <t xml:space="preserve">12.4199695587158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856800079346</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">12.4779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773954391479</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810892105103</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353921890259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596740722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111112594604</t>
+    <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910959243774</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">12.7922887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7493629455566</t>
+    <t xml:space="preserve">12.7493619918823</t>
   </si>
   <si>
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">12.4488725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781442642212</t>
@@ -914,25 +914,25 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.1913080215454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054563522339</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7191104888916</t>
+    <t xml:space="preserve">11.7191095352173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903282165527</t>
+    <t xml:space="preserve">11.5903301239014</t>
   </si>
   <si>
     <t xml:space="preserve">11.375693321228</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">13.3074150085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215604782104</t>
+    <t xml:space="preserve">13.2215595245361</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
@@ -998,43 +998,43 @@
     <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.135705947876</t>
+    <t xml:space="preserve">13.1357078552246</t>
   </si>
   <si>
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649766921997</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508321762085</t>
+    <t xml:space="preserve">13.6508312225342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361963272095</t>
+    <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
     <t xml:space="preserve">13.6937580108643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942474365234</t>
+    <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9143257141113</t>
+    <t xml:space="preserve">14.914324760437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351751327515</t>
+    <t xml:space="preserve">14.7351741790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
@@ -1046,58 +1046,58 @@
     <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977214813232</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289951324463</t>
+    <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498445510864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.973783493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811172485352</t>
+    <t xml:space="preserve">13.4811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915414810181</t>
+    <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">15.8548679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069900512695</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174152374268</t>
+    <t xml:space="preserve">15.3174161911011</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039014816284</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757173538208</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444417953491</t>
+    <t xml:space="preserve">15.9444437026978</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0788059234619</t>
+    <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683826446533</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309299468994</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7058353424072</t>
+    <t xml:space="preserve">16.7058372497559</t>
   </si>
   <si>
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247480392456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
@@ -1226,46 +1226,46 @@
     <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853624343872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417297363281</t>
+    <t xml:space="preserve">11.2417278289795</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313035964966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.7490634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925079345703</t>
+    <t xml:space="preserve">8.59925174713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40542984008789</t>
+    <t xml:space="preserve">9.40543079376221</t>
   </si>
   <si>
     <t xml:space="preserve">9.89809608459473</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1319,16 +1319,16 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822719573975</t>
+    <t xml:space="preserve">12.1822729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448173522949</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000299453735</t>
+    <t xml:space="preserve">11.6000308990479</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">12.7197246551514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4957847595215</t>
+    <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1361,43 +1361,43 @@
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4509983062744</t>
+    <t xml:space="preserve">12.4509973526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208784103394</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073656082153</t>
+    <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.793851852417</t>
+    <t xml:space="preserve">10.7938508987427</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8834257125854</t>
+    <t xml:space="preserve">10.8834266662598</t>
   </si>
   <si>
     <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
     <t xml:space="preserve">12.7645120620728</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -68975,7 +68975,7 @@
     </row>
     <row r="2566">
       <c r="A2566" s="1" t="n">
-        <v>46058.6854976852</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2566" t="n">
         <v>1482</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461597442627</t>
   </si>
   <si>
     <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
@@ -83,52 +83,52 @@
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783882141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875324249268</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.680778503418</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977247238159</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.719762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272497177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170593261719</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367033004761</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509469985962</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
     <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">11.1407556533813</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">11.2966794967651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031240463257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.2576999664307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">11.1251630783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.273289680481</t>
+    <t xml:space="preserve">11.2732906341553</t>
   </si>
   <si>
     <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942853927612</t>
+    <t xml:space="preserve">11.6942844390869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034315109253</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929336547852</t>
+    <t xml:space="preserve">11.5929346084595</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695457458496</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.3746404647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.6910057067871</t>
@@ -233,25 +233,25 @@
     <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6990346908569</t>
+    <t xml:space="preserve">11.6990356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2493810653687</t>
+    <t xml:space="preserve">11.2493801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625314712524</t>
+    <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201698303223</t>
+    <t xml:space="preserve">10.9201688766479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632722854614</t>
+    <t xml:space="preserve">11.7632703781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953901290894</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048940658569</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435678482056</t>
+    <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
     <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472124099731</t>
+    <t xml:space="preserve">11.7472133636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596277236938</t>
+    <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713003158569</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756856918335</t>
+    <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">11.5464735031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5545024871826</t>
+    <t xml:space="preserve">11.5545043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034191131592</t>
+    <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267700195312</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917446136475</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
     <t xml:space="preserve">11.5785932540894</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457345962524</t>
   </si>
   <si>
     <t xml:space="preserve">11.4581499099731</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">11.3858833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866203308105</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902667999268</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807619094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739182472229</t>
+    <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078035354614</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">12.1005115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7150936126709</t>
+    <t xml:space="preserve">11.7150945663452</t>
   </si>
   <si>
     <t xml:space="preserve">11.5304155349731</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.5903158187866</t>
   </si>
   <si>
     <t xml:space="preserve">12.9034652709961</t>
@@ -491,49 +491,49 @@
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859775543213</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487354278564</t>
+    <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144037246704</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.6625804901123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465196609497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379365921021</t>
+    <t xml:space="preserve">13.6379384994507</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">13.414231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733783721924</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028238296509</t>
+    <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3868284225464</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879758834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6079921722412</t>
+    <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6411333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5334205627441</t>
+    <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.3759956359863</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9062690734863</t>
+    <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068428039551</t>
+    <t xml:space="preserve">11.8068437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">11.823413848877</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">11.7571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476976394653</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.997407913208</t>
+    <t xml:space="preserve">11.9974098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814125061035</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">12.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719785690308</t>
+    <t xml:space="preserve">12.0719795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">12.171404838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396606445312</t>
+    <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022500991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4531116485596</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2211179733276</t>
+    <t xml:space="preserve">12.2211170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785409927368</t>
+    <t xml:space="preserve">12.3785419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796903610229</t>
+    <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045469284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.080265045166</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542591094971</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.353684425354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2874021530151</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">12.5525369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8839588165283</t>
+    <t xml:space="preserve">12.8839597702026</t>
   </si>
   <si>
     <t xml:space="preserve">12.8591012954712</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359659194946</t>
+    <t xml:space="preserve">12.5359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810901641846</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313760757446</t>
@@ -836,40 +836,40 @@
     <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225177764893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153787612915</t>
+    <t xml:space="preserve">13.2153797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242380142212</t>
+    <t xml:space="preserve">13.1242370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739511489868</t>
+    <t xml:space="preserve">13.1739492416382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9668130874634</t>
+    <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.7182483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353940963745</t>
+    <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111112594604</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205797195435</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">12.5776529312134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064352035522</t>
+    <t xml:space="preserve">12.7064361572266</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347270965576</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771644592285</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625286102295</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200922012329</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054553985596</t>
+    <t xml:space="preserve">12.1054544448853</t>
   </si>
   <si>
     <t xml:space="preserve">12.0196008682251</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478927612305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
     <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615468978882</t>
   </si>
   <si>
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498523712158</t>
+    <t xml:space="preserve">13.0498514175415</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639987945557</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">13.6079053878784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644872665405</t>
+    <t xml:space="preserve">13.2644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.135705947876</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508302688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225402832031</t>
+    <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942483901978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664487838745</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">15.3622035980225</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.287296295166</t>
+    <t xml:space="preserve">14.2872972488403</t>
   </si>
   <si>
     <t xml:space="preserve">14.1081447601318</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9737815856934</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394184112549</t>
+    <t xml:space="preserve">13.8394193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425088882446</t>
+    <t xml:space="preserve">14.2425079345703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216594696045</t>
+    <t xml:space="preserve">14.4216604232788</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903867721558</t>
+    <t xml:space="preserve">14.6903858184814</t>
   </si>
   <si>
     <t xml:space="preserve">14.6455984115601</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.2278413772583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0934762954712</t>
+    <t xml:space="preserve">15.0934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">15.183051109314</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
     <t xml:space="preserve">15.4965658187866</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382646560669</t>
+    <t xml:space="preserve">15.1382637023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.8695373535156</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1235942840576</t>
+    <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.586142539978</t>
+    <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
     <t xml:space="preserve">15.6309299468994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.541353225708</t>
+    <t xml:space="preserve">15.5413551330566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340194702148</t>
+    <t xml:space="preserve">16.0340175628662</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1199,55 +1199,55 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.481897354126</t>
+    <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923206329346</t>
+    <t xml:space="preserve">16.3923225402832</t>
   </si>
   <si>
     <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7205057144165</t>
+    <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247499465942</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
     <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8092994689941</t>
+    <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301498413086</t>
+    <t xml:space="preserve">12.6301488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8540897369385</t>
+    <t xml:space="preserve">12.8540887832642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.361421585083</t>
+    <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374845504761</t>
+    <t xml:space="preserve">12.1374835968018</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490615844727</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772457122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330772399902</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">8.77840137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
     <t xml:space="preserve">8.59925079345703</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809608459473</t>
+    <t xml:space="preserve">9.89809513092041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563972473145</t>
+    <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699129104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042760848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2865161895752</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969394683838</t>
+    <t xml:space="preserve">11.1969404220581</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">11.3760919570923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9583330154419</t>
+    <t xml:space="preserve">11.9583320617676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7791814804077</t>
+    <t xml:space="preserve">11.779182434082</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448192596436</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.6896066665649</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166360855103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">12.4957847595215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4062118530273</t>
+    <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
     <t xml:space="preserve">12.5405740737915</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">12.4509983062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2270584106445</t>
+    <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4208784103394</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104560852051</t>
+    <t xml:space="preserve">11.5104551315308</t>
   </si>
   <si>
     <t xml:space="preserve">11.1073656082153</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625782012939</t>
+    <t xml:space="preserve">11.0625772476196</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645120620728</t>
+    <t xml:space="preserve">12.7645130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5372667312622</t>
+    <t xml:space="preserve">11.5372676849365</t>
   </si>
   <si>
     <t xml:space="preserve">11.629566192627</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988208770752</t>
+    <t xml:space="preserve">11.3988199234009</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296268463135</t>
+    <t xml:space="preserve">11.0296277999878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373302459717</t>
+    <t xml:space="preserve">10.9373292922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.798882484436</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835411071777</t>
+    <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
     <t xml:space="preserve">10.291241645813</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0757761001587</t>
+    <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
     <t xml:space="preserve">11.1680755615234</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450317382812</t>
+    <t xml:space="preserve">10.8450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56813621521</t>
+    <t xml:space="preserve">10.5681371688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">11.8141622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99875831604</t>
+    <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1833543777466</t>
@@ -1948,6 +1948,9 @@
   <si>
     <t xml:space="preserve">19.6000003814697</t>
   </si>
+  <si>
+    <t xml:space="preserve">19.7000007629395</t>
+  </si>
 </sst>
 </file>
 
@@ -69105,7 +69108,7 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46065.685787037</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2571" t="n">
         <v>1216</v>
@@ -69126,6 +69129,32 @@
         <v>639</v>
       </c>
       <c r="H2571" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="1" t="n">
+        <v>46066.6911458333</v>
+      </c>
+      <c r="B2572" t="n">
+        <v>1435</v>
+      </c>
+      <c r="C2572" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2572" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475095748901</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617504119873</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553030014038</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136228561401</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461578369141</t>
+    <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082216262817</t>
@@ -74,58 +74,58 @@
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.078387260437</t>
+    <t xml:space="preserve">11.0783882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875333786011</t>
+    <t xml:space="preserve">11.1875343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495971679688</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807794570923</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977228164673</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146661758423</t>
+    <t xml:space="preserve">10.914665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116590499878</t>
+    <t xml:space="preserve">10.1116600036621</t>
   </si>
   <si>
     <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584367752075</t>
+    <t xml:space="preserve">10.1584358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611364364624</t>
+    <t xml:space="preserve">10.3611354827881</t>
   </si>
   <si>
     <t xml:space="preserve">10.5170602798462</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.556040763855</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638380050659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.140754699707</t>
   </si>
   <si>
     <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2576990127563</t>
+    <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
     <t xml:space="preserve">11.0627927780151</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685024261475</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942863464355</t>
+    <t xml:space="preserve">11.6942853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">11.6864900588989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4993801116943</t>
+    <t xml:space="preserve">11.499382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6630992889404</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929346084595</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">11.6007308959961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708984375</t>
+    <t xml:space="preserve">11.6708974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5695476531982</t>
+    <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
     <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910066604614</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742069244385</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961290359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793302536011</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7231245040894</t>
+    <t xml:space="preserve">11.7231225967407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">11.5625324249268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347999572754</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814989089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610546112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428289413452</t>
+    <t xml:space="preserve">11.6428279876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.8515977859497</t>
@@ -287,40 +287,40 @@
     <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968660354614</t>
+    <t xml:space="preserve">12.1968650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048950195312</t>
+    <t xml:space="preserve">12.2048959732056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435668945312</t>
+    <t xml:space="preserve">11.8435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.883713722229</t>
+    <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8676557540894</t>
+    <t xml:space="preserve">11.867654800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472143173218</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6187400817871</t>
@@ -329,40 +329,40 @@
     <t xml:space="preserve">11.8596258163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012186050415</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603647232056</t>
+    <t xml:space="preserve">12.0603637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479513168335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8756847381592</t>
+    <t xml:space="preserve">11.8756856918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.9238624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114500045776</t>
+    <t xml:space="preserve">11.811450958252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749467849731</t>
+    <t xml:space="preserve">11.6749477386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.5464744567871</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917465209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.4260301589966</t>
@@ -389,61 +389,61 @@
     <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822378158569</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581489562988</t>
+    <t xml:space="preserve">11.4581508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311534881592</t>
+    <t xml:space="preserve">11.7311525344849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2172622680664</t>
+    <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
     <t xml:space="preserve">11.3858842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778553009033</t>
   </si>
   <si>
     <t xml:space="preserve">11.3617944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420890808105</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6107110977173</t>
+    <t xml:space="preserve">11.610710144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4982957839966</t>
+    <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413511276245</t>
+    <t xml:space="preserve">11.2413501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807609558105</t>
+    <t xml:space="preserve">11.0807590484619</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734708786011</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">11.650857925415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
@@ -470,28 +470,28 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362758636475</t>
+    <t xml:space="preserve">12.0362768173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209548950195</t>
+    <t xml:space="preserve">12.2209568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457807540894</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903158187866</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859756469727</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844997406006</t>
@@ -500,67 +500,67 @@
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954343795776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654880523682</t>
+    <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136648178101</t>
+    <t xml:space="preserve">12.4136638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144037246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837608337402</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9516429901123</t>
+    <t xml:space="preserve">12.951642036438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479974746704</t>
+    <t xml:space="preserve">13.0479984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436149597168</t>
+    <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148050308228</t>
+    <t xml:space="preserve">13.3148031234741</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142293930054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319498062134</t>
+    <t xml:space="preserve">13.2319488525391</t>
   </si>
   <si>
     <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982320785522</t>
+    <t xml:space="preserve">13.2982330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939645767212</t>
+    <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442514419556</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">12.842529296875</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093891143799</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348194122314</t>
+    <t xml:space="preserve">12.7348184585571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762470245361</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">12.2294044494629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1879768371582</t>
+    <t xml:space="preserve">12.1879777908325</t>
   </si>
   <si>
     <t xml:space="preserve">11.8979825973511</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">11.5334215164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3759956359863</t>
+    <t xml:space="preserve">11.375994682312</t>
   </si>
   <si>
     <t xml:space="preserve">11.7737007141113</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
     <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823413848877</t>
+    <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
     <t xml:space="preserve">11.7571287155151</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382627487183</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0471220016479</t>
+    <t xml:space="preserve">12.0471229553223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6685352325439</t>
+    <t xml:space="preserve">12.6685342788696</t>
   </si>
   <si>
     <t xml:space="preserve">13.3396615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">12.9253854751587</t>
@@ -719,73 +719,73 @@
     <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3453989028931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6022510528564</t>
+    <t xml:space="preserve">12.6022520065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371162414551</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.569109916687</t>
+    <t xml:space="preserve">12.5691080093384</t>
   </si>
   <si>
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796894073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2045469284058</t>
+    <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2542600631714</t>
+    <t xml:space="preserve">12.2542610168457</t>
   </si>
   <si>
     <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3951120376587</t>
+    <t xml:space="preserve">12.395112991333</t>
   </si>
   <si>
     <t xml:space="preserve">12.303973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.751389503479</t>
+    <t xml:space="preserve">12.7513904571533</t>
   </si>
   <si>
     <t xml:space="preserve">12.8176736831665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8922452926636</t>
+    <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7928171157837</t>
+    <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608234405518</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4199695587158</t>
+    <t xml:space="preserve">12.4199705123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.5856790542603</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5359678268433</t>
+    <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">12.4613971710205</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810882568359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225177764893</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2153768539429</t>
+    <t xml:space="preserve">13.2153778076172</t>
   </si>
   <si>
     <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
     <t xml:space="preserve">13.4059457778931</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6353931427002</t>
+    <t xml:space="preserve">12.6353940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596769332886</t>
+    <t xml:space="preserve">12.7596759796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111103057861</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">13.0910959243774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493619918823</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.534725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917984008789</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">12.3630170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625276565552</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0195999145508</t>
+    <t xml:space="preserve">12.0195989608765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.933744430542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8478918075562</t>
+    <t xml:space="preserve">11.8478908538818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9766731262207</t>
+    <t xml:space="preserve">11.9766721725464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.7620363235474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615478515625</t>
+    <t xml:space="preserve">11.4615488052368</t>
   </si>
   <si>
     <t xml:space="preserve">11.7191095352173</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">11.5903291702271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756942749023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761827468872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.547402381897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3074131011963</t>
+    <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215614318848</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
     <t xml:space="preserve">13.6079053878784</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937580108643</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4664487838745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7799625396729</t>
+    <t xml:space="preserve">14.7799615859985</t>
   </si>
   <si>
     <t xml:space="preserve">14.914324760437</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1529331207275</t>
+    <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.2872953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.3768711090088</t>
@@ -1061,34 +1061,34 @@
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737825393677</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7946310043335</t>
+    <t xml:space="preserve">13.7946300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
     <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">15.1830530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.4965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517793655396</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">15.1382627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
     <t xml:space="preserve">15.0039005279541</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
     <t xml:space="preserve">16.3027458190918</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">16.0788078308105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683807373047</t>
+    <t xml:space="preserve">16.1683826446533</t>
   </si>
   <si>
     <t xml:space="preserve">16.1235961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.213171005249</t>
+    <t xml:space="preserve">16.2131729125977</t>
   </si>
   <si>
     <t xml:space="preserve">15.8996553421021</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">16.3475322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
     <t xml:space="preserve">16.6162586212158</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247489929199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1244,34 +1244,34 @@
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85330867767334</t>
+    <t xml:space="preserve">9.85330772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93963718414307</t>
+    <t xml:space="preserve">8.93963813781738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8386392593384</t>
+    <t xml:space="preserve">10.8386383056641</t>
   </si>
   <si>
     <t xml:space="preserve">11.3760919570923</t>
@@ -1322,49 +1322,49 @@
     <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
     <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
     <t xml:space="preserve">12.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406210899353</t>
+    <t xml:space="preserve">12.4062099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2718467712402</t>
+    <t xml:space="preserve">12.2718458175659</t>
   </si>
   <si>
     <t xml:space="preserve">12.4509973526001</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436635971069</t>
+    <t xml:space="preserve">12.9436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -69189,7 +69189,7 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46070.6911921296</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2574" t="n">
         <v>154</v>
@@ -69210,6 +69210,32 @@
         <v>646</v>
       </c>
       <c r="H2574" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46071.6341087963</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>196</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>640</v>
+      </c>
+      <c r="H2575" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">11.4681959152222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5617513656616</t>
+    <t xml:space="preserve">11.561749458313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553049087524</t>
+    <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512525558472</t>
+    <t xml:space="preserve">11.3512535095215</t>
   </si>
   <si>
     <t xml:space="preserve">11.4136219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526042938232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187166213989</t>
+    <t xml:space="preserve">11.2187185287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082216262817</t>
+    <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719398498535</t>
+    <t xml:space="preserve">11.1719408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600940704346</t>
+    <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961443901062</t>
+    <t xml:space="preserve">10.9614429473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.132960319519</t>
+    <t xml:space="preserve">11.1329593658447</t>
   </si>
   <si>
     <t xml:space="preserve">11.1875343322754</t>
@@ -95,61 +95,61 @@
     <t xml:space="preserve">10.5326538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495962142944</t>
+    <t xml:space="preserve">10.6495952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977237701416</t>
+    <t xml:space="preserve">10.7977247238159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9146671295166</t>
+    <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197618484497</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350469589233</t>
+    <t xml:space="preserve">10.1350479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.127251625061</t>
+    <t xml:space="preserve">10.1272506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584348678589</t>
   </si>
   <si>
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170593261719</t>
+    <t xml:space="preserve">10.5170621871948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8367033004761</t>
+    <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560426712036</t>
+    <t xml:space="preserve">10.5560417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509479522705</t>
+    <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638380050659</t>
+    <t xml:space="preserve">10.5638370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431497573853</t>
+    <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407566070557</t>
+    <t xml:space="preserve">11.1407556533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966804504395</t>
+    <t xml:space="preserve">11.2966785430908</t>
   </si>
   <si>
     <t xml:space="preserve">11.203125</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627927780151</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251649856567</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685014724731</t>
+    <t xml:space="preserve">12.0685033798218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942863464355</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864891052246</t>
+    <t xml:space="preserve">11.6864881515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49937915802</t>
+    <t xml:space="preserve">11.4993810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631011962891</t>
+    <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929365158081</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6007308959961</t>
+    <t xml:space="preserve">11.6007299423218</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708974838257</t>
@@ -203,37 +203,37 @@
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746433258057</t>
+    <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7552423477173</t>
+    <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742088317871</t>
+    <t xml:space="preserve">11.4742078781128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5063257217407</t>
+    <t xml:space="preserve">11.506326675415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070636749268</t>
+    <t xml:space="preserve">11.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158315658569</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537645339966</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">11.249382019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625324249268</t>
+    <t xml:space="preserve">11.5625343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347990036011</t>
+    <t xml:space="preserve">11.6347980499268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2814998626709</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">11.5384435653687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610555648804</t>
+    <t xml:space="preserve">11.1610565185547</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.289529800415</t>
+    <t xml:space="preserve">11.2895278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6428279876709</t>
+    <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515977859497</t>
+    <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795389175415</t>
+    <t xml:space="preserve">11.7953901290894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647481918335</t>
+    <t xml:space="preserve">12.1647472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1968679428101</t>
+    <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -311,55 +311,55 @@
     <t xml:space="preserve">11.8837146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640092849731</t>
+    <t xml:space="preserve">11.9640083312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472124099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669178009033</t>
+    <t xml:space="preserve">11.666916847229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121879577637</t>
+    <t xml:space="preserve">12.0121870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.0282468795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683917999268</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479494094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9238624572754</t>
+    <t xml:space="preserve">11.923864364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8275079727173</t>
+    <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588888168335</t>
+    <t xml:space="preserve">11.6588878631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">11.5545034408569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034181594849</t>
+    <t xml:space="preserve">11.8034191131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.6267690658569</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917436599731</t>
+    <t xml:space="preserve">11.8917455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260301589966</t>
+    <t xml:space="preserve">11.4260311126709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.522385597229</t>
+    <t xml:space="preserve">11.5223865509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822378158569</t>
+    <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">11.2092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457355499268</t>
+    <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7311525344849</t>
+    <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
@@ -425,43 +425,43 @@
     <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866231918335</t>
+    <t xml:space="preserve">11.5866212844849</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902677536011</t>
+    <t xml:space="preserve">11.4902687072754</t>
   </si>
   <si>
     <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734689712524</t>
+    <t xml:space="preserve">11.2734699249268</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.650857925415</t>
+    <t xml:space="preserve">11.6508569717407</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078035354614</t>
+    <t xml:space="preserve">11.9078025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1005115509033</t>
+    <t xml:space="preserve">12.1005125045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.7150945663452</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362749099731</t>
   </si>
   <si>
     <t xml:space="preserve">12.2289838790894</t>
@@ -479,61 +479,61 @@
     <t xml:space="preserve">12.2209558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.445782661438</t>
+    <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.590313911438</t>
+    <t xml:space="preserve">12.5903129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.8713483810425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.585976600647</t>
+    <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1845006942749</t>
+    <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654870986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530727386475</t>
+    <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144018173218</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6625804901123</t>
+    <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.224645614624</t>
+    <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837627410889</t>
+    <t xml:space="preserve">12.9837617874146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516429901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479974746704</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">12.9436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
     <t xml:space="preserve">13.3148040771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.414231300354</t>
+    <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319507598877</t>
+    <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733764648438</t>
+    <t xml:space="preserve">13.2733774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271076202393</t>
+    <t xml:space="preserve">12.6271085739136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105365753174</t>
+    <t xml:space="preserve">12.6105375289917</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768207550049</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442533493042</t>
+    <t xml:space="preserve">12.5442523956299</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868284225464</t>
+    <t xml:space="preserve">12.3868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.527681350708</t>
+    <t xml:space="preserve">12.5276803970337</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093881607056</t>
+    <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259582519531</t>
+    <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348194122314</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">12.7762470245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265338897705</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288307189941</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548337936401</t>
+    <t xml:space="preserve">12.1548347473145</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">11.6079902648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6411333084106</t>
+    <t xml:space="preserve">11.641131401062</t>
   </si>
   <si>
     <t xml:space="preserve">11.5334215164185</t>
@@ -641,61 +641,61 @@
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7737016677856</t>
+    <t xml:space="preserve">11.773699760437</t>
   </si>
   <si>
     <t xml:space="preserve">11.906268119812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8068418502808</t>
+    <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488441467285</t>
+    <t xml:space="preserve">11.7488451004028</t>
   </si>
   <si>
     <t xml:space="preserve">11.8234148025513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571296691895</t>
+    <t xml:space="preserve">11.7571287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9476957321167</t>
+    <t xml:space="preserve">11.947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">12.0056953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9974098205566</t>
+    <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554075241089</t>
+    <t xml:space="preserve">12.0554084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814134597778</t>
+    <t xml:space="preserve">11.8814115524292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819852828979</t>
+    <t xml:space="preserve">11.7819871902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305509567261</t>
+    <t xml:space="preserve">12.0305519104004</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0719776153564</t>
+    <t xml:space="preserve">12.0719785690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.171404838562</t>
+    <t xml:space="preserve">12.1714057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465482711792</t>
+    <t xml:space="preserve">12.1465492248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">13.0082406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.925386428833</t>
+    <t xml:space="preserve">12.9253854751587</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756732940674</t>
+    <t xml:space="preserve">12.8756723403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453998565674</t>
+    <t xml:space="preserve">12.3453989028931</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4531126022339</t>
+    <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">12.221118927002</t>
+    <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
     <t xml:space="preserve">12.3785419464111</t>
@@ -743,31 +743,31 @@
     <t xml:space="preserve">12.2376890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968360900879</t>
+    <t xml:space="preserve">12.0968351364136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0885496139526</t>
+    <t xml:space="preserve">12.088550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796894073486</t>
+    <t xml:space="preserve">12.1796903610229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.080265045166</t>
+    <t xml:space="preserve">12.0802640914917</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962614059448</t>
+    <t xml:space="preserve">12.1962623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536853790283</t>
+    <t xml:space="preserve">12.3536863327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874011993408</t>
+    <t xml:space="preserve">12.2874021530151</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">12.8591022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679605484009</t>
+    <t xml:space="preserve">12.7679615020752</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">12.792818069458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5608243942261</t>
+    <t xml:space="preserve">12.5608224868774</t>
   </si>
   <si>
     <t xml:space="preserve">12.4199695587158</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">12.5856800079346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.477970123291</t>
+    <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773935317993</t>
+    <t xml:space="preserve">12.5773944854736</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4613981246948</t>
+    <t xml:space="preserve">12.4613971710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.0496683120728</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">13.3810873031616</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313760757446</t>
+    <t xml:space="preserve">13.3313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230895996094</t>
+    <t xml:space="preserve">13.3230905532837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225168228149</t>
+    <t xml:space="preserve">13.4225158691406</t>
   </si>
   <si>
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242370605469</t>
+    <t xml:space="preserve">13.1242389678955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413818359375</t>
+    <t xml:space="preserve">13.0413827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059457778931</t>
+    <t xml:space="preserve">13.4059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325235366821</t>
+    <t xml:space="preserve">13.1325244903564</t>
   </si>
   <si>
     <t xml:space="preserve">13.1739501953125</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182483673096</t>
+    <t xml:space="preserve">12.7182493209839</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">12.5111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910959243774</t>
+    <t xml:space="preserve">13.0910968780518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922887802124</t>
+    <t xml:space="preserve">12.7922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635084152222</t>
+    <t xml:space="preserve">12.6635074615479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205797195435</t>
+    <t xml:space="preserve">12.6205806732178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4059438705444</t>
+    <t xml:space="preserve">12.4059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5776538848877</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">12.7064342498779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5347270965576</t>
+    <t xml:space="preserve">12.5347261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4488725662231</t>
+    <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
     <t xml:space="preserve">12.4917993545532</t>
@@ -911,34 +911,34 @@
     <t xml:space="preserve">12.8781433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3630170822144</t>
+    <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342357635498</t>
+    <t xml:space="preserve">12.2342367172241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1483821868896</t>
+    <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771644592285</t>
+    <t xml:space="preserve">12.2771635055542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0625276565552</t>
+    <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1913089752197</t>
+    <t xml:space="preserve">12.191309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200902938843</t>
+    <t xml:space="preserve">12.3200912475586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1054544448853</t>
+    <t xml:space="preserve">12.1054553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0196008682251</t>
+    <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337453842163</t>
+    <t xml:space="preserve">11.9337463378906</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908195495605</t>
+    <t xml:space="preserve">11.8908205032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620372772217</t>
+    <t xml:space="preserve">11.762038230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049650192261</t>
+    <t xml:space="preserve">11.8049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5903301239014</t>
+    <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3756923675537</t>
+    <t xml:space="preserve">11.375693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6761837005615</t>
+    <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474014282227</t>
+    <t xml:space="preserve">11.5474004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0498514175415</t>
+    <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639978408813</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786336898804</t>
+    <t xml:space="preserve">13.1786346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2215614318848</t>
+    <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079053878784</t>
+    <t xml:space="preserve">13.6079063415527</t>
   </si>
   <si>
     <t xml:space="preserve">13.2644882202148</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.564977645874</t>
+    <t xml:space="preserve">13.5649785995483</t>
   </si>
   <si>
     <t xml:space="preserve">13.6508312225342</t>
@@ -1013,25 +1013,25 @@
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937589645386</t>
+    <t xml:space="preserve">13.6937599182129</t>
   </si>
   <si>
     <t xml:space="preserve">13.8225412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942483901978</t>
+    <t xml:space="preserve">13.9942493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4664468765259</t>
+    <t xml:space="preserve">14.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3622035980225</t>
+    <t xml:space="preserve">15.3622026443481</t>
   </si>
   <si>
     <t xml:space="preserve">14.7799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.914324760437</t>
+    <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.7351741790771</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">14.1529331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872972488403</t>
+    <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081447601318</t>
+    <t xml:space="preserve">14.1081457138062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977205276489</t>
+    <t xml:space="preserve">14.1977224349976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768711090088</t>
+    <t xml:space="preserve">14.3768701553345</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">14.0633583068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8842067718506</t>
+    <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498435974121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.973783493042</t>
+    <t xml:space="preserve">13.9737815856934</t>
   </si>
   <si>
     <t xml:space="preserve">13.660267829895</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050552368164</t>
+    <t xml:space="preserve">13.7050561904907</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4363298416138</t>
+    <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259056091309</t>
+    <t xml:space="preserve">13.5259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4811162948608</t>
+    <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">13.3915405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706920623779</t>
+    <t xml:space="preserve">13.5706911087036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8394193649292</t>
+    <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
     <t xml:space="preserve">14.2425079345703</t>
@@ -1118,52 +1118,52 @@
     <t xml:space="preserve">14.6455984115601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8548679351807</t>
+    <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069910049438</t>
+    <t xml:space="preserve">15.4069919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174161911011</t>
+    <t xml:space="preserve">15.3174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.227840423584</t>
+    <t xml:space="preserve">15.2278394699097</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1830530166626</t>
+    <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4965658187866</t>
+    <t xml:space="preserve">15.496563911438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4517784118652</t>
+    <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
     <t xml:space="preserve">15.0486879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1382627487183</t>
+    <t xml:space="preserve">15.1382646560669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8695383071899</t>
+    <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0039005279541</t>
+    <t xml:space="preserve">15.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757183074951</t>
+    <t xml:space="preserve">15.6757164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444427490234</t>
+    <t xml:space="preserve">15.9444446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027458190918</t>
+    <t xml:space="preserve">16.3027439117432</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996553421021</t>
+    <t xml:space="preserve">15.8996572494507</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861406326294</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309299468994</t>
+    <t xml:space="preserve">15.6309309005737</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5413551330566</t>
+    <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">16.0340175628662</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">16.4818954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923225402832</t>
+    <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162586212158</t>
+    <t xml:space="preserve">16.6162605285645</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8247480392456</t>
+    <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9591131210327</t>
+    <t xml:space="preserve">14.959114074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.8093004226685</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">12.0479078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6301488876343</t>
+    <t xml:space="preserve">12.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.8540878295898</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">12.5853614807129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374835968018</t>
+    <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
     <t xml:space="preserve">11.2417287826538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3313035964966</t>
+    <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7490634918213</t>
+    <t xml:space="preserve">10.749062538147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772457122803</t>
+    <t xml:space="preserve">10.0772466659546</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77840137481689</t>
+    <t xml:space="preserve">8.77840232849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59925174713135</t>
+    <t xml:space="preserve">8.59924983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18149185180664</t>
+    <t xml:space="preserve">9.18149089813232</t>
   </si>
   <si>
     <t xml:space="preserve">9.40542984008789</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355478286743</t>
+    <t xml:space="preserve">10.4355487823486</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">10.2563982009888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5699129104614</t>
+    <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
     <t xml:space="preserve">10.7042751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865171432495</t>
+    <t xml:space="preserve">11.2865161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730014801025</t>
+    <t xml:space="preserve">10.9730024337769</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">11.9583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.779182434082</t>
+    <t xml:space="preserve">11.7791814804077</t>
   </si>
   <si>
     <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926961898804</t>
+    <t xml:space="preserve">12.0926952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1822710037231</t>
+    <t xml:space="preserve">12.1822719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6448173522949</t>
+    <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896076202393</t>
+    <t xml:space="preserve">11.6896057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6000308990479</t>
+    <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343940734863</t>
+    <t xml:space="preserve">11.7343950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239688873291</t>
+    <t xml:space="preserve">11.8239698410034</t>
   </si>
   <si>
     <t xml:space="preserve">11.8687572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0031204223633</t>
+    <t xml:space="preserve">12.003119468689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166360855103</t>
+    <t xml:space="preserve">12.3166351318359</t>
   </si>
   <si>
     <t xml:space="preserve">12.7197246551514</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405731201172</t>
+    <t xml:space="preserve">12.5405740737915</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4208793640137</t>
+    <t xml:space="preserve">11.420880317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">11.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1521520614624</t>
+    <t xml:space="preserve">11.1521530151367</t>
   </si>
   <si>
     <t xml:space="preserve">10.9282140731812</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">10.8834257125854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0625772476196</t>
+    <t xml:space="preserve">11.0625782012939</t>
   </si>
   <si>
     <t xml:space="preserve">12.9436635971069</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">11.7680130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834169387817</t>
+    <t xml:space="preserve">11.5834159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3988199234009</t>
+    <t xml:space="preserve">11.3988208770752</t>
   </si>
   <si>
     <t xml:space="preserve">11.7218637466431</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">11.35267162323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3065214157104</t>
+    <t xml:space="preserve">11.3065223693848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.21422290802</t>
+    <t xml:space="preserve">11.2142238616943</t>
   </si>
   <si>
     <t xml:space="preserve">10.5219879150391</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">11.2603731155396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373292922974</t>
+    <t xml:space="preserve">10.9373302459717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.798882484436</t>
+    <t xml:space="preserve">10.7988815307617</t>
   </si>
   <si>
     <t xml:space="preserve">10.6604356765747</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.3835401535034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291241645813</t>
+    <t xml:space="preserve">10.2912425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3373918533325</t>
+    <t xml:space="preserve">10.3373908996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.7527322769165</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">11.075777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680755615234</t>
+    <t xml:space="preserve">11.1680746078491</t>
   </si>
   <si>
     <t xml:space="preserve">10.9834785461426</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">10.8911809921265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8450307846069</t>
+    <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
     <t xml:space="preserve">10.5681371688843</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">11.4449691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">11.491117477417</t>
+    <t xml:space="preserve">11.4911184310913</t>
   </si>
   <si>
     <t xml:space="preserve">11.1219263076782</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">12.0710897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760417938232</t>
+    <t xml:space="preserve">11.9760427474976</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">11.785945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5008029937744</t>
+    <t xml:space="preserve">11.5008020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3107051849365</t>
+    <t xml:space="preserve">11.3107061386108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2156591415405</t>
+    <t xml:space="preserve">11.2156581878662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1206102371216</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7404193878174</t>
+    <t xml:space="preserve">10.7404184341431</t>
   </si>
   <si>
     <t xml:space="preserve">10.6453704833984</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">10.4552745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8354654312134</t>
+    <t xml:space="preserve">10.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.3602266311646</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">10.2651786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0255632400513</t>
+    <t xml:space="preserve">11.025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4057540893555</t>
+    <t xml:space="preserve">11.4057550430298</t>
   </si>
   <si>
     <t xml:space="preserve">11.4532785415649</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">12.213662147522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.3582305908203</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.7879428863525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0235662460327</t>
+    <t xml:space="preserve">12.0235652923584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.64137840271</t>
+    <t xml:space="preserve">12.6413774490356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938529968262</t>
+    <t xml:space="preserve">12.5938539505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.8136281967163</t>
@@ -69238,7 +69238,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.4785300926</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>353</v>
@@ -69259,6 +69259,32 @@
         <v>632</v>
       </c>
       <c r="H2576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.5786574074</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>118</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>641</v>
+      </c>
+      <c r="H2577" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475076675415</t>
+    <t xml:space="preserve">11.6475086212158</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617504119873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6553039550781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3512535095215</t>
+    <t xml:space="preserve">11.3512544631958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136228561401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526042938232</t>
+    <t xml:space="preserve">11.4526033401489</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5461587905884</t>
+    <t xml:space="preserve">11.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
     <t xml:space="preserve">11.0082206726074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1719408035278</t>
+    <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
     <t xml:space="preserve">10.8600931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9614429473877</t>
+    <t xml:space="preserve">10.9614448547363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783863067627</t>
+    <t xml:space="preserve">11.078387260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329593658447</t>
+    <t xml:space="preserve">11.1329584121704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5326538085938</t>
+    <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807813644409</t>
+    <t xml:space="preserve">10.6807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7977247238159</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7197608947754</t>
+    <t xml:space="preserve">10.7197618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065643310547</t>
+    <t xml:space="preserve">10.3065624237061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272506713867</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
     <t xml:space="preserve">10.1584348678589</t>
@@ -128,61 +128,61 @@
     <t xml:space="preserve">10.3611373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170621871948</t>
+    <t xml:space="preserve">10.5170602798462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
     <t xml:space="preserve">10.7509460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638370513916</t>
+    <t xml:space="preserve">10.5638389587402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7431507110596</t>
+    <t xml:space="preserve">10.7431497573853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966785430908</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.203125</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
     <t xml:space="preserve">11.257698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627937316895</t>
+    <t xml:space="preserve">11.0627946853638</t>
   </si>
   <si>
     <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1251649856567</t>
+    <t xml:space="preserve">11.1251640319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.2732915878296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0685033798218</t>
+    <t xml:space="preserve">12.0685014724731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034324645996</t>
+    <t xml:space="preserve">11.8034334182739</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864881515503</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
     <t xml:space="preserve">11.4993810653687</t>
@@ -191,79 +191,79 @@
     <t xml:space="preserve">11.6631002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929355621338</t>
+    <t xml:space="preserve">11.5929365158081</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708974838257</t>
+    <t xml:space="preserve">11.6708965301514</t>
   </si>
   <si>
     <t xml:space="preserve">11.5695466995239</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3746423721313</t>
+    <t xml:space="preserve">11.374641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910057067871</t>
+    <t xml:space="preserve">11.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">11.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4742078781128</t>
+    <t xml:space="preserve">11.4742088317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.506326675415</t>
+    <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070636749268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961280822754</t>
+    <t xml:space="preserve">11.9961271286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0443058013916</t>
+    <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158315658569</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7793312072754</t>
+    <t xml:space="preserve">11.7793302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537654876709</t>
+    <t xml:space="preserve">11.3537664413452</t>
   </si>
   <si>
     <t xml:space="preserve">11.7873611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723123550415</t>
+    <t xml:space="preserve">11.7231245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625343322754</t>
+    <t xml:space="preserve">11.5625333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6347980499268</t>
+    <t xml:space="preserve">11.6347990036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2814998626709</t>
+    <t xml:space="preserve">11.2814979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201717376709</t>
+    <t xml:space="preserve">10.9201707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610565185547</t>
+    <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
     <t xml:space="preserve">11.1771154403687</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">11.4501209259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632713317871</t>
+    <t xml:space="preserve">11.7632722854614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2895278930664</t>
+    <t xml:space="preserve">11.2895288467407</t>
   </si>
   <si>
     <t xml:space="preserve">11.6428289413452</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">11.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953901290894</t>
+    <t xml:space="preserve">11.795389175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771606445312</t>
+    <t xml:space="preserve">12.2771615982056</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194789886475</t>
+    <t xml:space="preserve">11.8194780349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1647472381592</t>
+    <t xml:space="preserve">12.1647481918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1968660354614</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">12.2048969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3253393173218</t>
+    <t xml:space="preserve">12.3253383636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8837146759033</t>
+    <t xml:space="preserve">11.8837156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640083312988</t>
+    <t xml:space="preserve">11.9640102386475</t>
   </si>
   <si>
     <t xml:space="preserve">11.7472124099731</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">11.6187391281128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8596267700195</t>
+    <t xml:space="preserve">11.8596248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282468795776</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713012695312</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479494094849</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.923864364624</t>
+    <t xml:space="preserve">11.9238634109497</t>
   </si>
   <si>
     <t xml:space="preserve">11.827507019043</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464744567871</t>
+    <t xml:space="preserve">11.5464754104614</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545034408569</t>
@@ -380,46 +380,46 @@
     <t xml:space="preserve">11.899772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8917455673218</t>
+    <t xml:space="preserve">11.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4260311126709</t>
+    <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5785932540894</t>
+    <t xml:space="preserve">11.5785913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.5223846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4822387695312</t>
+    <t xml:space="preserve">11.4822359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.3457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581508636475</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180021286011</t>
+    <t xml:space="preserve">11.4180011749268</t>
   </si>
   <si>
     <t xml:space="preserve">11.2172632217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858833312988</t>
+    <t xml:space="preserve">11.3858823776245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.377854347229</t>
+    <t xml:space="preserve">11.3778533935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3617944717407</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
     <t xml:space="preserve">11.4420900344849</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866212844849</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4902687072754</t>
+    <t xml:space="preserve">11.4902696609497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143556594849</t>
+    <t xml:space="preserve">11.5143566131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.2413511276245</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">11.0807609558105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734699249268</t>
+    <t xml:space="preserve">11.2734708786011</t>
   </si>
   <si>
     <t xml:space="preserve">12.2450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7391834259033</t>
+    <t xml:space="preserve">11.739182472229</t>
   </si>
   <si>
     <t xml:space="preserve">11.9078025817871</t>
@@ -470,61 +470,61 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362749099731</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289838790894</t>
+    <t xml:space="preserve">12.2289848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2209558486938</t>
+    <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903129577637</t>
+    <t xml:space="preserve">12.5903148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034662246704</t>
+    <t xml:space="preserve">12.9034652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713493347168</t>
   </si>
   <si>
     <t xml:space="preserve">13.5859756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1844987869263</t>
+    <t xml:space="preserve">13.1844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">13.2487363815308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895435333252</t>
+    <t xml:space="preserve">12.8954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3654870986938</t>
+    <t xml:space="preserve">12.3654861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2530736923218</t>
+    <t xml:space="preserve">12.2530746459961</t>
   </si>
   <si>
     <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144027709961</t>
+    <t xml:space="preserve">12.6144018173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465215682983</t>
+    <t xml:space="preserve">12.646520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9275550842285</t>
+    <t xml:space="preserve">12.9275541305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472595214844</t>
+    <t xml:space="preserve">12.8472585678101</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436130523682</t>
   </si>
   <si>
     <t xml:space="preserve">13.6379375457764</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">13.2319498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982320785522</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">12.8342447280884</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6271085739136</t>
+    <t xml:space="preserve">12.6271076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.6105365753174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939655303955</t>
+    <t xml:space="preserve">12.5939664840698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">12.5028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5276803970337</t>
+    <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425302505493</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">12.8093891143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8259592056274</t>
+    <t xml:space="preserve">12.8259601593018</t>
   </si>
   <si>
     <t xml:space="preserve">12.7348194122314</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">12.8011035919189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116840362549</t>
+    <t xml:space="preserve">12.4116830825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1548347473145</t>
+    <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
     <t xml:space="preserve">12.2294034957886</t>
@@ -641,46 +641,46 @@
     <t xml:space="preserve">11.3759965896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773699760437</t>
+    <t xml:space="preserve">11.7737016677856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.906268119812</t>
+    <t xml:space="preserve">11.9062690734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8068428039551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7488451004028</t>
+    <t xml:space="preserve">11.7488431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8234148025513</t>
+    <t xml:space="preserve">11.823413848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7571287155151</t>
+    <t xml:space="preserve">11.7571296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947696685791</t>
+    <t xml:space="preserve">11.9476957321167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0056953430176</t>
+    <t xml:space="preserve">12.0056943893433</t>
   </si>
   <si>
     <t xml:space="preserve">11.9974088668823</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0554084777832</t>
+    <t xml:space="preserve">12.0554075241089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814115524292</t>
+    <t xml:space="preserve">11.8814125061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7902708053589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7819871902466</t>
+    <t xml:space="preserve">11.7819862365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0305519104004</t>
+    <t xml:space="preserve">12.0305509567261</t>
   </si>
   <si>
     <t xml:space="preserve">12.1382637023926</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">12.0471220016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1714057922363</t>
+    <t xml:space="preserve">12.1714038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1465492248535</t>
+    <t xml:space="preserve">12.1465482711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1051206588745</t>
@@ -704,22 +704,22 @@
     <t xml:space="preserve">12.6685352325439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396615982056</t>
+    <t xml:space="preserve">13.3396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0082406997681</t>
+    <t xml:space="preserve">13.0082397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9253854751587</t>
+    <t xml:space="preserve">12.925386428833</t>
   </si>
   <si>
     <t xml:space="preserve">12.9088144302368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8756723403931</t>
+    <t xml:space="preserve">12.8756742477417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453989028931</t>
+    <t xml:space="preserve">12.3454008102417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6022510528564</t>
@@ -728,25 +728,25 @@
     <t xml:space="preserve">12.4531116485596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371152877808</t>
+    <t xml:space="preserve">12.3371143341064</t>
   </si>
   <si>
     <t xml:space="preserve">12.2211179733276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3785419464111</t>
+    <t xml:space="preserve">12.3785409927368</t>
   </si>
   <si>
     <t xml:space="preserve">12.5691089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2376890182495</t>
+    <t xml:space="preserve">12.2376880645752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0968351364136</t>
+    <t xml:space="preserve">12.0968360900879</t>
   </si>
   <si>
-    <t xml:space="preserve">12.088550567627</t>
+    <t xml:space="preserve">12.0885496139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.1796903610229</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">12.2045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0802640914917</t>
+    <t xml:space="preserve">12.0802631378174</t>
   </si>
   <si>
     <t xml:space="preserve">12.2542600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1962623596191</t>
+    <t xml:space="preserve">12.1962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3536863327026</t>
+    <t xml:space="preserve">12.3536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2874021530151</t>
+    <t xml:space="preserve">12.2874011993408</t>
   </si>
   <si>
     <t xml:space="preserve">12.4282550811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395112991333</t>
+    <t xml:space="preserve">12.3951139450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.3039741516113</t>
@@ -782,25 +782,25 @@
     <t xml:space="preserve">12.7513914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8176736831665</t>
+    <t xml:space="preserve">12.8176727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5525369644165</t>
+    <t xml:space="preserve">12.5525379180908</t>
   </si>
   <si>
     <t xml:space="preserve">12.883957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8591022491455</t>
+    <t xml:space="preserve">12.8591012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7679615020752</t>
+    <t xml:space="preserve">12.7679605484009</t>
   </si>
   <si>
     <t xml:space="preserve">12.8922443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.792818069458</t>
+    <t xml:space="preserve">12.7928171157837</t>
   </si>
   <si>
     <t xml:space="preserve">12.5608224868774</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">12.4779682159424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5773944854736</t>
+    <t xml:space="preserve">12.5773954391479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5359668731689</t>
@@ -827,67 +827,67 @@
     <t xml:space="preserve">13.0496683120728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3810873031616</t>
+    <t xml:space="preserve">13.3810892105103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3313751220703</t>
+    <t xml:space="preserve">13.3313760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230905532837</t>
+    <t xml:space="preserve">13.3230895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4225158691406</t>
+    <t xml:space="preserve">13.4225168228149</t>
   </si>
   <si>
     <t xml:space="preserve">13.2153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1242389678955</t>
+    <t xml:space="preserve">13.1242380142212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0413827896118</t>
+    <t xml:space="preserve">13.0413818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4059448242188</t>
+    <t xml:space="preserve">13.4059438705444</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1325244903564</t>
+    <t xml:space="preserve">13.1325225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1739501953125</t>
+    <t xml:space="preserve">13.1739511489868</t>
   </si>
   <si>
     <t xml:space="preserve">12.9668121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7182493209839</t>
+    <t xml:space="preserve">12.7182474136353</t>
   </si>
   <si>
     <t xml:space="preserve">12.6353931427002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7596759796143</t>
+    <t xml:space="preserve">12.7596750259399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4696826934814</t>
+    <t xml:space="preserve">12.4696836471558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111103057861</t>
+    <t xml:space="preserve">12.5111112594604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910968780518</t>
+    <t xml:space="preserve">13.0910949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7922878265381</t>
+    <t xml:space="preserve">12.7922897338867</t>
   </si>
   <si>
     <t xml:space="preserve">12.7493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6635074615479</t>
+    <t xml:space="preserve">12.6635084152222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6205806732178</t>
+    <t xml:space="preserve">12.6205816268921</t>
   </si>
   <si>
     <t xml:space="preserve">12.4059448242188</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">12.5776538848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7064342498779</t>
+    <t xml:space="preserve">12.7064352035522</t>
   </si>
   <si>
     <t xml:space="preserve">12.5347261428833</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">12.4488716125488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4917993545532</t>
+    <t xml:space="preserve">12.4917984008789</t>
   </si>
   <si>
     <t xml:space="preserve">12.8781433105469</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">12.3630180358887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2342367172241</t>
+    <t xml:space="preserve">12.2342357635498</t>
   </si>
   <si>
     <t xml:space="preserve">12.1483812332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771635055542</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">12.0625267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">12.191309928894</t>
+    <t xml:space="preserve">12.1913089752197</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3200912475586</t>
+    <t xml:space="preserve">12.3200902938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.1054553985596</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.0195999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337463378906</t>
+    <t xml:space="preserve">11.9337453842163</t>
   </si>
   <si>
     <t xml:space="preserve">11.8478918075562</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">11.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8908205032349</t>
+    <t xml:space="preserve">11.8908195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762038230896</t>
+    <t xml:space="preserve">11.7620372772217</t>
   </si>
   <si>
     <t xml:space="preserve">11.4615478515625</t>
@@ -959,43 +959,43 @@
     <t xml:space="preserve">11.7191104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8049659729004</t>
+    <t xml:space="preserve">11.8049650192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.5903282165527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.375693321228</t>
+    <t xml:space="preserve">11.3756923675537</t>
   </si>
   <si>
     <t xml:space="preserve">11.6761846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5474004745483</t>
+    <t xml:space="preserve">11.5474014282227</t>
   </si>
   <si>
     <t xml:space="preserve">13.0498523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639978408813</t>
+    <t xml:space="preserve">12.9639987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0069236755371</t>
+    <t xml:space="preserve">13.0069246292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3074140548706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1786346435547</t>
+    <t xml:space="preserve">13.1786336898804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2215604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6079063415527</t>
+    <t xml:space="preserve">13.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2644882202148</t>
+    <t xml:space="preserve">13.2644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.1357069015503</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">13.350341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5649785995483</t>
+    <t xml:space="preserve">13.564977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6508312225342</t>
+    <t xml:space="preserve">13.6508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">13.4361953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937599182129</t>
+    <t xml:space="preserve">13.6937589645386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8225412368774</t>
+    <t xml:space="preserve">13.8225402832031</t>
   </si>
   <si>
     <t xml:space="preserve">13.9942493438721</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">14.9143257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7351741790771</t>
+    <t xml:space="preserve">14.7351751327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.6008100509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1529331207275</t>
+    <t xml:space="preserve">14.1529321670532</t>
   </si>
   <si>
     <t xml:space="preserve">14.287296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1081457138062</t>
+    <t xml:space="preserve">14.1081447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1977224349976</t>
+    <t xml:space="preserve">14.1977205276489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3768701553345</t>
+    <t xml:space="preserve">14.3768711090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.928994178772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0633583068848</t>
+    <t xml:space="preserve">14.0633573532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8842058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498435974121</t>
+    <t xml:space="preserve">13.7498426437378</t>
   </si>
   <si>
     <t xml:space="preserve">13.9737815856934</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">13.7946310043335</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7050561904907</t>
+    <t xml:space="preserve">13.7050552368164</t>
   </si>
   <si>
     <t xml:space="preserve">13.4363288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5259046554565</t>
+    <t xml:space="preserve">13.5259056091309</t>
   </si>
   <si>
     <t xml:space="preserve">13.4811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3915405273438</t>
+    <t xml:space="preserve">13.3915414810181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5706911087036</t>
+    <t xml:space="preserve">13.5706920623779</t>
   </si>
   <si>
     <t xml:space="preserve">13.8394184112549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2425079345703</t>
+    <t xml:space="preserve">14.2425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0185689926147</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">14.3320846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4216604232788</t>
+    <t xml:space="preserve">14.4216594696045</t>
   </si>
   <si>
     <t xml:space="preserve">14.556022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903858184814</t>
+    <t xml:space="preserve">14.6903867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6455984115601</t>
+    <t xml:space="preserve">14.6455993652344</t>
   </si>
   <si>
     <t xml:space="preserve">15.854868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4069919586182</t>
+    <t xml:space="preserve">15.4069910049438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3174142837524</t>
+    <t xml:space="preserve">15.3174152374268</t>
   </si>
   <si>
     <t xml:space="preserve">15.2726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2278394699097</t>
+    <t xml:space="preserve">15.227840423584</t>
   </si>
   <si>
     <t xml:space="preserve">15.0934762954712</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">15.1830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.496563911438</t>
+    <t xml:space="preserve">15.4965667724609</t>
   </si>
   <si>
     <t xml:space="preserve">15.4517774581909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0486879348755</t>
+    <t xml:space="preserve">15.0486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">15.1382646560669</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">14.8695373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0038995742798</t>
+    <t xml:space="preserve">15.0039005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6757164001465</t>
+    <t xml:space="preserve">15.6757183074951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9444446563721</t>
+    <t xml:space="preserve">15.9444427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3027439117432</t>
+    <t xml:space="preserve">16.3027458190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0788078308105</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">16.213171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8996572494507</t>
+    <t xml:space="preserve">15.8996553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861406326294</t>
+    <t xml:space="preserve">15.586142539978</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6309309005737</t>
+    <t xml:space="preserve">15.6309289932251</t>
   </si>
   <si>
     <t xml:space="preserve">15.541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0340175628662</t>
+    <t xml:space="preserve">16.0340194702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7058353424072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3475322723389</t>
+    <t xml:space="preserve">16.3475341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4818954467773</t>
+    <t xml:space="preserve">16.481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">16.3923206329346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6162605285645</t>
+    <t xml:space="preserve">16.6162586212158</t>
   </si>
   <si>
     <t xml:space="preserve">15.7205038070679</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">14.8247499465942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.959114074707</t>
+    <t xml:space="preserve">14.9591131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093004226685</t>
+    <t xml:space="preserve">12.8092994689941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0479078292847</t>
+    <t xml:space="preserve">12.047908782959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6301498413086</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">12.3614225387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5853614807129</t>
+    <t xml:space="preserve">12.5853605270386</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374845504761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2417287826538</t>
+    <t xml:space="preserve">11.2417297363281</t>
   </si>
   <si>
     <t xml:space="preserve">11.3313045501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749062538147</t>
+    <t xml:space="preserve">10.7490615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0772466659546</t>
+    <t xml:space="preserve">10.0772476196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.85330867767334</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">8.93963718414307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59924983978271</t>
+    <t xml:space="preserve">8.59925079345703</t>
   </si>
   <si>
     <t xml:space="preserve">9.18149089813232</t>
@@ -1268,37 +1268,37 @@
     <t xml:space="preserve">9.40542984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89809513092041</t>
+    <t xml:space="preserve">9.89809608459473</t>
   </si>
   <si>
     <t xml:space="preserve">10.3011856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355487823486</t>
+    <t xml:space="preserve">10.4355478286743</t>
   </si>
   <si>
     <t xml:space="preserve">10.3907613754272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563982009888</t>
+    <t xml:space="preserve">10.2563972473145</t>
   </si>
   <si>
     <t xml:space="preserve">10.5699119567871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7042751312256</t>
+    <t xml:space="preserve">10.7042741775513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2865161895752</t>
+    <t xml:space="preserve">11.2865171432495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9730024337769</t>
+    <t xml:space="preserve">10.9730014801025</t>
   </si>
   <si>
     <t xml:space="preserve">11.0177898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1969404220581</t>
+    <t xml:space="preserve">11.1969413757324</t>
   </si>
   <si>
     <t xml:space="preserve">10.8386392593384</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">11.9135456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0926952362061</t>
+    <t xml:space="preserve">12.0926961898804</t>
   </si>
   <si>
     <t xml:space="preserve">12.1822719573975</t>
@@ -1325,28 +1325,28 @@
     <t xml:space="preserve">11.6448183059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896057128906</t>
+    <t xml:space="preserve">11.6896066665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.6000299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7343950271606</t>
+    <t xml:space="preserve">11.7343940734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8239698410034</t>
+    <t xml:space="preserve">11.8239688873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8687572479248</t>
+    <t xml:space="preserve">11.8687562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.003119468689</t>
+    <t xml:space="preserve">12.0031204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3166351318359</t>
+    <t xml:space="preserve">12.3166341781616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7197246551514</t>
+    <t xml:space="preserve">12.7197237014771</t>
   </si>
   <si>
     <t xml:space="preserve">12.4957857131958</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">12.406210899353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5405740737915</t>
+    <t xml:space="preserve">12.5405731201172</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749362945557</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">12.2270593643188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.420880317688</t>
+    <t xml:space="preserve">11.4208793640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5552425384521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5104551315308</t>
+    <t xml:space="preserve">11.5104560852051</t>
   </si>
   <si>
     <t xml:space="preserve">11.107364654541</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">12.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7645130157471</t>
+    <t xml:space="preserve">12.7645120620728</t>
   </si>
   <si>
     <t xml:space="preserve">11.4656677246094</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">11.629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7680130004883</t>
+    <t xml:space="preserve">11.768012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5834159851074</t>
+    <t xml:space="preserve">11.5834169387817</t>
   </si>
   <si>
     <t xml:space="preserve">11.3988208770752</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">10.7065849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0296277999878</t>
+    <t xml:space="preserve">11.0296268463135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2603731155396</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">10.4296903610229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3835401535034</t>
+    <t xml:space="preserve">10.3835411071777</t>
   </si>
   <si>
     <t xml:space="preserve">10.2912425994873</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">10.7527322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.075777053833</t>
+    <t xml:space="preserve">11.0757761001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1680746078491</t>
+    <t xml:space="preserve">11.1680755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9834785461426</t>
+    <t xml:space="preserve">10.9834775924683</t>
   </si>
   <si>
     <t xml:space="preserve">10.8911809921265</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">10.8450317382812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5681371688843</t>
+    <t xml:space="preserve">10.56813621521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4758396148682</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">11.9987573623657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1833543777466</t>
+    <t xml:space="preserve">12.1833534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910568237305</t>
@@ -69264,7 +69264,7 @@
     </row>
     <row r="2577">
       <c r="A2577" s="1" t="n">
-        <v>46073.5786574074</v>
+        <v>46073.3333333333</v>
       </c>
       <c r="B2577" t="n">
         <v>118</v>
@@ -69285,6 +69285,32 @@
         <v>641</v>
       </c>
       <c r="H2577" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46076.629525463</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>1867</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>631</v>
+      </c>
+      <c r="H2578" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -38,130 +38,130 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6475086212158</t>
+    <t xml:space="preserve">11.6475076675415</t>
   </si>
   <si>
     <t xml:space="preserve">TYA.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4681959152222</t>
+    <t xml:space="preserve">11.4681968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.561749458313</t>
+    <t xml:space="preserve">11.5617513656616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6553039550781</t>
+    <t xml:space="preserve">11.6553049087524</t>
   </si>
   <si>
     <t xml:space="preserve">11.3512525558472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4136219024658</t>
+    <t xml:space="preserve">11.4136238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4526033401489</t>
+    <t xml:space="preserve">11.4526023864746</t>
   </si>
   <si>
     <t xml:space="preserve">11.5461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2187185287476</t>
+    <t xml:space="preserve">11.2187175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0082197189331</t>
+    <t xml:space="preserve">11.0082216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095714569092</t>
+    <t xml:space="preserve">11.1095724105835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1719398498535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8600931167603</t>
+    <t xml:space="preserve">10.8600940704346</t>
   </si>
   <si>
     <t xml:space="preserve">10.961443901062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0783853530884</t>
+    <t xml:space="preserve">11.0783863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1329584121704</t>
+    <t xml:space="preserve">11.132960319519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1875343322754</t>
+    <t xml:space="preserve">11.1875333786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.5326528549194</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6495952606201</t>
+    <t xml:space="preserve">10.6495962142944</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6807804107666</t>
+    <t xml:space="preserve">10.6807813644409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7977228164673</t>
+    <t xml:space="preserve">10.7977237701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9146661758423</t>
   </si>
   <si>
-    <t xml:space="preserve">10.719762802124</t>
+    <t xml:space="preserve">10.7197608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065633773804</t>
+    <t xml:space="preserve">10.3065643310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1116580963135</t>
+    <t xml:space="preserve">10.1116590499878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1350479125977</t>
+    <t xml:space="preserve">10.1350469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1272525787354</t>
+    <t xml:space="preserve">10.127251625061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1584358215332</t>
+    <t xml:space="preserve">10.1584367752075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3611373901367</t>
+    <t xml:space="preserve">10.3611364364624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5170602798462</t>
+    <t xml:space="preserve">10.5170612335205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8367052078247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5560417175293</t>
+    <t xml:space="preserve">10.5560426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7509460449219</t>
+    <t xml:space="preserve">10.7509469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5638399124146</t>
+    <t xml:space="preserve">10.5638360977173</t>
   </si>
   <si>
     <t xml:space="preserve">10.7431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1407556533813</t>
+    <t xml:space="preserve">11.1407566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2966794967651</t>
+    <t xml:space="preserve">11.2966804504395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2031240463257</t>
+    <t xml:space="preserve">11.2031259536743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.257698059082</t>
+    <t xml:space="preserve">11.2576990127563</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0627946853638</t>
+    <t xml:space="preserve">11.0627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0472011566162</t>
+    <t xml:space="preserve">11.0472021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.1251640319824</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">12.0685024261475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6942834854126</t>
+    <t xml:space="preserve">11.6942863464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8034334182739</t>
+    <t xml:space="preserve">11.8034324645996</t>
   </si>
   <si>
     <t xml:space="preserve">12.0840950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6864900588989</t>
+    <t xml:space="preserve">11.6864891052246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.499382019043</t>
+    <t xml:space="preserve">11.4993801116943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631002426147</t>
+    <t xml:space="preserve">11.6631011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5929346084595</t>
+    <t xml:space="preserve">11.5929355621338</t>
   </si>
   <si>
     <t xml:space="preserve">11.6007308959961</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">11.3746423721313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6910047531128</t>
+    <t xml:space="preserve">11.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755241394043</t>
+    <t xml:space="preserve">11.7552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.4742088317871</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">11.5063257217407</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7070655822754</t>
+    <t xml:space="preserve">11.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9961290359497</t>
+    <t xml:space="preserve">11.9961280822754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0443048477173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9158325195312</t>
+    <t xml:space="preserve">11.9158334732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.7793312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3537664413452</t>
+    <t xml:space="preserve">11.3537654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7873611450195</t>
+    <t xml:space="preserve">11.7873601913452</t>
   </si>
   <si>
     <t xml:space="preserve">11.723123550415</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">11.6990346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">11.249382019043</t>
+    <t xml:space="preserve">11.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5625333786011</t>
+    <t xml:space="preserve">11.5625314712524</t>
   </si>
   <si>
     <t xml:space="preserve">11.6347990036011</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">11.2814998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5384435653687</t>
+    <t xml:space="preserve">11.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9201707839966</t>
+    <t xml:space="preserve">10.9201698303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610555648804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1771154403687</t>
+    <t xml:space="preserve">11.177116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.450119972229</t>
+    <t xml:space="preserve">11.4501190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7632703781128</t>
+    <t xml:space="preserve">11.7632713317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.2895288467407</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">11.6428289413452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8515968322754</t>
+    <t xml:space="preserve">11.8515977859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953882217407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2771615982056</t>
+    <t xml:space="preserve">12.2771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8194780349731</t>
+    <t xml:space="preserve">11.8194789886475</t>
   </si>
   <si>
     <t xml:space="preserve">12.1647472381592</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">12.1968660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2048959732056</t>
+    <t xml:space="preserve">12.2048950195312</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253393173218</t>
@@ -311,40 +311,40 @@
     <t xml:space="preserve">11.883713722229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.867654800415</t>
+    <t xml:space="preserve">11.8676557540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9640111923218</t>
+    <t xml:space="preserve">11.9640092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7472133636475</t>
+    <t xml:space="preserve">11.7472143173218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666916847229</t>
+    <t xml:space="preserve">11.6669158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6187400817871</t>
+    <t xml:space="preserve">11.6187410354614</t>
   </si>
   <si>
     <t xml:space="preserve">11.8596267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0121870040894</t>
+    <t xml:space="preserve">12.0121879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0282459259033</t>
+    <t xml:space="preserve">12.028244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713003158569</t>
+    <t xml:space="preserve">11.7713012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0603637695312</t>
+    <t xml:space="preserve">12.0603647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0683946609497</t>
+    <t xml:space="preserve">12.0683937072754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479513168335</t>
+    <t xml:space="preserve">11.9479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">11.8756847381592</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">11.827507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811448097229</t>
+    <t xml:space="preserve">11.8114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6588878631592</t>
+    <t xml:space="preserve">11.6588869094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.6749467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5464735031128</t>
+    <t xml:space="preserve">11.5464744567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5545043945312</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">11.8034181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6267690658569</t>
+    <t xml:space="preserve">11.6267681121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.899772644043</t>
+    <t xml:space="preserve">11.8997735977173</t>
   </si>
   <si>
     <t xml:space="preserve">11.8917446136475</t>
@@ -386,49 +386,49 @@
     <t xml:space="preserve">11.4260301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.578592300415</t>
+    <t xml:space="preserve">11.5785932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5223865509033</t>
+    <t xml:space="preserve">11.522385597229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2092342376709</t>
+    <t xml:space="preserve">11.2092332839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3457365036011</t>
+    <t xml:space="preserve">11.3457355499268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4581499099731</t>
+    <t xml:space="preserve">11.4581489562988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7311534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180011749268</t>
+    <t xml:space="preserve">11.4180021286011</t>
   </si>
   <si>
     <t xml:space="preserve">11.217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3858842849731</t>
+    <t xml:space="preserve">11.3858852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3778533935547</t>
+    <t xml:space="preserve">11.377854347229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.361795425415</t>
+    <t xml:space="preserve">11.3617935180664</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4420909881592</t>
+    <t xml:space="preserve">11.4420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.610710144043</t>
+    <t xml:space="preserve">11.6107110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5866222381592</t>
+    <t xml:space="preserve">11.5866231918335</t>
   </si>
   <si>
     <t xml:space="preserve">11.4982967376709</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">11.4902677536011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5143566131592</t>
+    <t xml:space="preserve">11.5143556594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2413520812988</t>
+    <t xml:space="preserve">11.2413511276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734708786011</t>
+    <t xml:space="preserve">11.2734689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2450437545776</t>
+    <t xml:space="preserve">12.2450428009033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508569717407</t>
+    <t xml:space="preserve">11.6508588790894</t>
   </si>
   <si>
     <t xml:space="preserve">11.7391834259033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9078025817871</t>
+    <t xml:space="preserve">11.9078044891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.1005115509033</t>
@@ -470,37 +470,37 @@
     <t xml:space="preserve">11.5304145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0362768173218</t>
+    <t xml:space="preserve">12.0362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2289848327637</t>
+    <t xml:space="preserve">12.2289838790894</t>
   </si>
   <si>
     <t xml:space="preserve">12.2209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457817077637</t>
+    <t xml:space="preserve">12.445782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903148651123</t>
+    <t xml:space="preserve">12.590313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9034652709961</t>
+    <t xml:space="preserve">12.9034662246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8713483810425</t>
+    <t xml:space="preserve">12.8713474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5859775543213</t>
+    <t xml:space="preserve">13.585976600647</t>
   </si>
   <si>
     <t xml:space="preserve">13.1844987869263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2487335205078</t>
+    <t xml:space="preserve">13.2487354278564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8954362869263</t>
+    <t xml:space="preserve">12.895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.3654861450195</t>
@@ -509,58 +509,58 @@
     <t xml:space="preserve">12.2530736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4136638641357</t>
+    <t xml:space="preserve">12.4136648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6144008636475</t>
+    <t xml:space="preserve">12.6144027709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.662579536438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.646520614624</t>
+    <t xml:space="preserve">12.6465215682983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9275550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8472585678101</t>
+    <t xml:space="preserve">12.8472595214844</t>
   </si>
   <si>
     <t xml:space="preserve">13.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9837617874146</t>
+    <t xml:space="preserve">12.9837608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.951642036438</t>
+    <t xml:space="preserve">12.9516410827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479965209961</t>
+    <t xml:space="preserve">13.0479974746704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9436140060425</t>
+    <t xml:space="preserve">12.9436149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6379384994507</t>
+    <t xml:space="preserve">13.6379375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3148040771484</t>
+    <t xml:space="preserve">13.3148050308228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4142303466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2319488525391</t>
+    <t xml:space="preserve">13.2319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2733774185181</t>
+    <t xml:space="preserve">13.2733764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982330322266</t>
+    <t xml:space="preserve">13.2982320785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.240234375</t>
+    <t xml:space="preserve">13.2402353286743</t>
   </si>
   <si>
     <t xml:space="preserve">12.8342447280884</t>
@@ -569,70 +569,70 @@
     <t xml:space="preserve">12.6271066665649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6105375289917</t>
+    <t xml:space="preserve">12.610538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768217086792</t>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5442523956299</t>
+    <t xml:space="preserve">12.5442514419556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5028247833252</t>
+    <t xml:space="preserve">12.5028257369995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3868274688721</t>
+    <t xml:space="preserve">12.3868284225464</t>
   </si>
   <si>
     <t xml:space="preserve">12.527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425312042236</t>
+    <t xml:space="preserve">12.8425302505493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8093891143799</t>
+    <t xml:space="preserve">12.8093881607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.8259592056274</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7348184585571</t>
+    <t xml:space="preserve">12.7348194122314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7762460708618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8011026382446</t>
+    <t xml:space="preserve">12.8011016845703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265338897705</t>
+    <t xml:space="preserve">12.7265329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4116849899292</t>
+    <t xml:space="preserve">12.4116840362549</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288297653198</t>
+    <t xml:space="preserve">12.3288288116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.1548337936401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2294044494629</t>
+    <t xml:space="preserve">12.2294034957886</t>
   </si>
   <si>
     <t xml:space="preserve">12.1879758834839</t>
   </si>
 